--- a/feedback-daily.xlsx
+++ b/feedback-daily.xlsx
@@ -2869,7 +2869,7 @@
         <v>复验那么久了，为什么还不能正常上架？</v>
       </c>
       <c r="I77" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J77" t="str">
         <v>手机</v>
@@ -3576,7 +3576,7 @@
         <v>上架拍照并未有明显的溢胶 退回来溢胶很奇怪 摸一下就掉了 麻烦发一下后验的质检视频</v>
       </c>
       <c r="I99" t="str">
-        <v>待处理</v>
+        <v>处理中</v>
       </c>
       <c r="J99" t="str">
         <v>手机</v>

--- a/feedback-daily.xlsx
+++ b/feedback-daily.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J238"/>
+  <dimension ref="A1:L238"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -409,6 +409,8 @@
     <col min="8" max="8" width="40.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,6 +444,12 @@
       <c r="J1" t="str">
         <v>类目</v>
       </c>
+      <c r="K1" t="str">
+        <v>业务线</v>
+      </c>
+      <c r="L1" t="str">
+        <v>中心仓</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -474,6 +482,12 @@
       <c r="J2" t="str">
         <v>手机</v>
       </c>
+      <c r="K2" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L2" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -506,6 +520,12 @@
       <c r="J3" t="str">
         <v>智能手表</v>
       </c>
+      <c r="K3" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L3" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -538,6 +558,12 @@
       <c r="J4" t="str">
         <v>手机</v>
       </c>
+      <c r="K4" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L4" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -570,6 +596,12 @@
       <c r="J5" t="str">
         <v>手机</v>
       </c>
+      <c r="K5" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L5" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -602,6 +634,12 @@
       <c r="J6" t="str">
         <v>手机</v>
       </c>
+      <c r="K6" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L6" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -634,6 +672,12 @@
       <c r="J7" t="str">
         <v>手机</v>
       </c>
+      <c r="K7" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L7" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -666,6 +710,12 @@
       <c r="J8" t="str">
         <v>手机</v>
       </c>
+      <c r="K8" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L8" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -698,6 +748,12 @@
       <c r="J9" t="str">
         <v>手机</v>
       </c>
+      <c r="K9" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L9" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -730,6 +786,12 @@
       <c r="J10" t="str">
         <v>手机</v>
       </c>
+      <c r="K10" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L10" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -762,6 +824,12 @@
       <c r="J11" t="str">
         <v>手机</v>
       </c>
+      <c r="K11" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L11" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -794,6 +862,12 @@
       <c r="J12" t="str">
         <v>手机</v>
       </c>
+      <c r="K12" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L12" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -826,6 +900,12 @@
       <c r="J13" t="str">
         <v>手机</v>
       </c>
+      <c r="K13" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L13" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -858,6 +938,12 @@
       <c r="J14" t="str">
         <v>手机</v>
       </c>
+      <c r="K14" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L14" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -890,6 +976,12 @@
       <c r="J15" t="str">
         <v>手机</v>
       </c>
+      <c r="K15" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L15" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -922,6 +1014,12 @@
       <c r="J16" t="str">
         <v>手机</v>
       </c>
+      <c r="K16" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L16" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -954,6 +1052,12 @@
       <c r="J17" t="str">
         <v>手机</v>
       </c>
+      <c r="K17" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L17" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -986,6 +1090,12 @@
       <c r="J18" t="str">
         <v>手机</v>
       </c>
+      <c r="K18" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L18" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1018,6 +1128,12 @@
       <c r="J19" t="str">
         <v>手机</v>
       </c>
+      <c r="K19" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L19" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1050,6 +1166,12 @@
       <c r="J20" t="str">
         <v>手机</v>
       </c>
+      <c r="K20" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L20" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1082,6 +1204,12 @@
       <c r="J21" t="str">
         <v>耳机/耳麦</v>
       </c>
+      <c r="K21" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L21" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1114,6 +1242,12 @@
       <c r="J22" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K22" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L22" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1146,6 +1280,12 @@
       <c r="J23" t="str">
         <v>手机</v>
       </c>
+      <c r="K23" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L23" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1178,6 +1318,12 @@
       <c r="J24" t="str">
         <v>手机</v>
       </c>
+      <c r="K24" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L24" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1210,6 +1356,12 @@
       <c r="J25" t="str">
         <v>手机</v>
       </c>
+      <c r="K25" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L25" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1242,6 +1394,12 @@
       <c r="J26" t="str">
         <v>手机</v>
       </c>
+      <c r="K26" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L26" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1274,6 +1432,12 @@
       <c r="J27" t="str">
         <v>手机</v>
       </c>
+      <c r="K27" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L27" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1306,6 +1470,12 @@
       <c r="J28" t="str">
         <v>手机</v>
       </c>
+      <c r="K28" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L28" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1338,6 +1508,12 @@
       <c r="J29" t="str">
         <v>手机</v>
       </c>
+      <c r="K29" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L29" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1370,6 +1546,12 @@
       <c r="J30" t="str">
         <v>手机</v>
       </c>
+      <c r="K30" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L30" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1402,6 +1584,12 @@
       <c r="J31" t="str">
         <v>手机</v>
       </c>
+      <c r="K31" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L31" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1434,6 +1622,12 @@
       <c r="J32" t="str">
         <v>手机</v>
       </c>
+      <c r="K32" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L32" t="str">
+        <v>深圳-迟恭彦（自质检2.0）</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1466,6 +1660,12 @@
       <c r="J33" t="str">
         <v>手机</v>
       </c>
+      <c r="K33" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L33" t="str">
+        <v>深圳-迟恭彦（自质检2.0）</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1498,6 +1698,12 @@
       <c r="J34" t="str">
         <v>手机</v>
       </c>
+      <c r="K34" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L34" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1530,6 +1736,12 @@
       <c r="J35" t="str">
         <v>手机</v>
       </c>
+      <c r="K35" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L35" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1562,6 +1774,12 @@
       <c r="J36" t="str">
         <v>手机</v>
       </c>
+      <c r="K36" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L36" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1594,6 +1812,12 @@
       <c r="J37" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K37" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L37" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1626,6 +1850,12 @@
       <c r="J38" t="str">
         <v>手机</v>
       </c>
+      <c r="K38" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L38" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1658,6 +1888,12 @@
       <c r="J39" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K39" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L39" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1690,6 +1926,12 @@
       <c r="J40" t="str">
         <v>手机</v>
       </c>
+      <c r="K40" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L40" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1722,6 +1964,12 @@
       <c r="J41" t="str">
         <v>手机</v>
       </c>
+      <c r="K41" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L41" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1754,6 +2002,12 @@
       <c r="J42" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K42" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L42" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1786,6 +2040,12 @@
       <c r="J43" t="str">
         <v>手机</v>
       </c>
+      <c r="K43" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L43" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1818,6 +2078,12 @@
       <c r="J44" t="str">
         <v>手机</v>
       </c>
+      <c r="K44" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L44" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1850,6 +2116,12 @@
       <c r="J45" t="str">
         <v>手机</v>
       </c>
+      <c r="K45" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L45" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1882,6 +2154,12 @@
       <c r="J46" t="str">
         <v>手机</v>
       </c>
+      <c r="K46" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L46" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1914,6 +2192,12 @@
       <c r="J47" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K47" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L47" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1946,6 +2230,12 @@
       <c r="J48" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K48" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L48" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1978,6 +2268,12 @@
       <c r="J49" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K49" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L49" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2010,6 +2306,12 @@
       <c r="J50" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K50" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L50" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2042,6 +2344,12 @@
       <c r="J51" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K51" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L51" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2074,6 +2382,12 @@
       <c r="J52" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K52" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L52" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2106,6 +2420,12 @@
       <c r="J53" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K53" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L53" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2138,6 +2458,12 @@
       <c r="J54" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K54" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L54" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2170,6 +2496,12 @@
       <c r="J55" t="str">
         <v>手机</v>
       </c>
+      <c r="K55" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L55" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2202,6 +2534,12 @@
       <c r="J56" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K56" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L56" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2234,6 +2572,12 @@
       <c r="J57" t="str">
         <v>手机</v>
       </c>
+      <c r="K57" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L57" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2266,6 +2610,12 @@
       <c r="J58" t="str">
         <v>手机</v>
       </c>
+      <c r="K58" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L58" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2298,6 +2648,12 @@
       <c r="J59" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K59" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L59" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2330,6 +2686,12 @@
       <c r="J60" t="str">
         <v>手机</v>
       </c>
+      <c r="K60" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L60" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2362,6 +2724,12 @@
       <c r="J61" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K61" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L61" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2394,6 +2762,12 @@
       <c r="J62" t="str">
         <v>手机</v>
       </c>
+      <c r="K62" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L62" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2426,6 +2800,12 @@
       <c r="J63" t="str">
         <v>手机</v>
       </c>
+      <c r="K63" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L63" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2458,6 +2838,12 @@
       <c r="J64" t="str">
         <v>手机</v>
       </c>
+      <c r="K64" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L64" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2490,6 +2876,12 @@
       <c r="J65" t="str">
         <v>手机</v>
       </c>
+      <c r="K65" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L65" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2522,6 +2914,12 @@
       <c r="J66" t="str">
         <v>手机</v>
       </c>
+      <c r="K66" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L66" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -2554,6 +2952,12 @@
       <c r="J67" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K67" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L67" t="str">
+        <v>福建-魏女（已验机2.0）</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -2586,6 +2990,12 @@
       <c r="J68" t="str">
         <v>手机</v>
       </c>
+      <c r="K68" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L68" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -2618,6 +3028,12 @@
       <c r="J69" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K69" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L69" t="str">
+        <v>青岛后验中心仓</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -2650,6 +3066,12 @@
       <c r="J70" t="str">
         <v>手机</v>
       </c>
+      <c r="K70" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L70" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -2682,6 +3104,12 @@
       <c r="J71" t="str">
         <v>手机</v>
       </c>
+      <c r="K71" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L71" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -2714,6 +3142,12 @@
       <c r="J72" t="str">
         <v>手机</v>
       </c>
+      <c r="K72" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L72" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -2746,6 +3180,12 @@
       <c r="J73" t="str">
         <v>手机</v>
       </c>
+      <c r="K73" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L73" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -2778,6 +3218,12 @@
       <c r="J74" t="str">
         <v>智能手表</v>
       </c>
+      <c r="K74" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L74" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -2810,6 +3256,12 @@
       <c r="J75" t="str">
         <v>手机</v>
       </c>
+      <c r="K75" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L75" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -2842,6 +3294,12 @@
       <c r="J76" t="str">
         <v>手机</v>
       </c>
+      <c r="K76" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L76" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -2869,10 +3327,16 @@
         <v>复验那么久了，为什么还不能正常上架？</v>
       </c>
       <c r="I77" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
       <c r="J77" t="str">
         <v>手机</v>
+      </c>
+      <c r="K77" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L77" t="str">
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="78">
@@ -2906,6 +3370,12 @@
       <c r="J78" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K78" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L78" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -2938,6 +3408,12 @@
       <c r="J79" t="str">
         <v>手机</v>
       </c>
+      <c r="K79" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L79" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -2970,6 +3446,12 @@
       <c r="J80" t="str">
         <v>手机</v>
       </c>
+      <c r="K80" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L80" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -3002,6 +3484,12 @@
       <c r="J81" t="str">
         <v>手机</v>
       </c>
+      <c r="K81" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L81" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="82" xml:space="preserve">
       <c r="A82" t="str">
@@ -3035,6 +3523,12 @@
       <c r="J82" t="str">
         <v>手机</v>
       </c>
+      <c r="K82" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L82" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -3067,6 +3561,12 @@
       <c r="J83" t="str">
         <v>手机</v>
       </c>
+      <c r="K83" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L83" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="84" xml:space="preserve">
       <c r="A84" t="str">
@@ -3100,6 +3600,12 @@
       <c r="J84" t="str">
         <v>手机</v>
       </c>
+      <c r="K84" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L84" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -3132,6 +3638,12 @@
       <c r="J85" t="str">
         <v>手机</v>
       </c>
+      <c r="K85" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L85" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -3164,6 +3676,12 @@
       <c r="J86" t="str">
         <v>手机</v>
       </c>
+      <c r="K86" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L86" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -3196,6 +3714,12 @@
       <c r="J87" t="str">
         <v>手机</v>
       </c>
+      <c r="K87" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L87" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -3228,6 +3752,12 @@
       <c r="J88" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K88" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L88" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -3260,6 +3790,12 @@
       <c r="J89" t="str">
         <v>手机</v>
       </c>
+      <c r="K89" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L89" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -3292,6 +3828,12 @@
       <c r="J90" t="str">
         <v>手机</v>
       </c>
+      <c r="K90" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L90" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -3324,6 +3866,12 @@
       <c r="J91" t="str">
         <v>手机</v>
       </c>
+      <c r="K91" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L91" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -3356,6 +3904,12 @@
       <c r="J92" t="str">
         <v>手机</v>
       </c>
+      <c r="K92" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L92" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -3388,6 +3942,12 @@
       <c r="J93" t="str">
         <v>手机</v>
       </c>
+      <c r="K93" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L93" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -3420,6 +3980,12 @@
       <c r="J94" t="str">
         <v>手机</v>
       </c>
+      <c r="K94" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L94" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -3452,6 +4018,12 @@
       <c r="J95" t="str">
         <v>手机</v>
       </c>
+      <c r="K95" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L95" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -3484,6 +4056,12 @@
       <c r="J96" t="str">
         <v>手机</v>
       </c>
+      <c r="K96" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L96" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -3516,6 +4094,12 @@
       <c r="J97" t="str">
         <v>手机</v>
       </c>
+      <c r="K97" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L97" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="98" xml:space="preserve">
       <c r="A98" t="str">
@@ -3549,6 +4133,12 @@
       <c r="J98" t="str">
         <v>手机</v>
       </c>
+      <c r="K98" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L98" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -3576,10 +4166,16 @@
         <v>上架拍照并未有明显的溢胶 退回来溢胶很奇怪 摸一下就掉了 麻烦发一下后验的质检视频</v>
       </c>
       <c r="I99" t="str">
-        <v>处理中</v>
+        <v>待处理</v>
       </c>
       <c r="J99" t="str">
         <v>手机</v>
+      </c>
+      <c r="K99" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L99" t="str">
+        <v>杭州库</v>
       </c>
     </row>
     <row r="100">
@@ -3613,6 +4209,12 @@
       <c r="J100" t="str">
         <v>手机</v>
       </c>
+      <c r="K100" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L100" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -3645,6 +4247,12 @@
       <c r="J101" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K101" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L101" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -3677,6 +4285,12 @@
       <c r="J102" t="str">
         <v>手机</v>
       </c>
+      <c r="K102" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L102" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -3709,6 +4323,12 @@
       <c r="J103" t="str">
         <v>手机</v>
       </c>
+      <c r="K103" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L103" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -3741,6 +4361,12 @@
       <c r="J104" t="str">
         <v>手机</v>
       </c>
+      <c r="K104" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L104" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -3773,6 +4399,12 @@
       <c r="J105" t="str">
         <v>手机</v>
       </c>
+      <c r="K105" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L105" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -3805,6 +4437,12 @@
       <c r="J106" t="str">
         <v>手机</v>
       </c>
+      <c r="K106" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L106" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -3837,6 +4475,12 @@
       <c r="J107" t="str">
         <v>手机</v>
       </c>
+      <c r="K107" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L107" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -3869,6 +4513,12 @@
       <c r="J108" t="str">
         <v>手机</v>
       </c>
+      <c r="K108" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L108" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -3901,6 +4551,12 @@
       <c r="J109" t="str">
         <v>手机</v>
       </c>
+      <c r="K109" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L109" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -3933,6 +4589,12 @@
       <c r="J110" t="str">
         <v>手机</v>
       </c>
+      <c r="K110" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L110" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -3965,6 +4627,12 @@
       <c r="J111" t="str">
         <v>手机</v>
       </c>
+      <c r="K111" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L111" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -3997,6 +4665,12 @@
       <c r="J112" t="str">
         <v>手机</v>
       </c>
+      <c r="K112" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L112" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -4029,6 +4703,12 @@
       <c r="J113" t="str">
         <v>手机</v>
       </c>
+      <c r="K113" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L113" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4061,6 +4741,12 @@
       <c r="J114" t="str">
         <v>手机</v>
       </c>
+      <c r="K114" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L114" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -4093,6 +4779,12 @@
       <c r="J115" t="str">
         <v>智能手表</v>
       </c>
+      <c r="K115" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L115" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -4125,6 +4817,12 @@
       <c r="J116" t="str">
         <v>手机</v>
       </c>
+      <c r="K116" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L116" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -4157,6 +4855,12 @@
       <c r="J117" t="str">
         <v>手机</v>
       </c>
+      <c r="K117" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L117" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -4189,6 +4893,12 @@
       <c r="J118" t="str">
         <v>手机</v>
       </c>
+      <c r="K118" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L118" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -4221,6 +4931,12 @@
       <c r="J119" t="str">
         <v>手机</v>
       </c>
+      <c r="K119" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L119" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -4253,6 +4969,12 @@
       <c r="J120" t="str">
         <v>手机</v>
       </c>
+      <c r="K120" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L120" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -4285,6 +5007,12 @@
       <c r="J121" t="str">
         <v>手机</v>
       </c>
+      <c r="K121" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L121" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -4317,6 +5045,12 @@
       <c r="J122" t="str">
         <v>手机</v>
       </c>
+      <c r="K122" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L122" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -4349,6 +5083,12 @@
       <c r="J123" t="str">
         <v>手机</v>
       </c>
+      <c r="K123" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L123" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -4381,6 +5121,12 @@
       <c r="J124" t="str">
         <v>手机</v>
       </c>
+      <c r="K124" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L124" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -4413,6 +5159,12 @@
       <c r="J125" t="str">
         <v>手机</v>
       </c>
+      <c r="K125" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L125" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -4445,6 +5197,12 @@
       <c r="J126" t="str">
         <v>手机</v>
       </c>
+      <c r="K126" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L126" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -4477,6 +5235,12 @@
       <c r="J127" t="str">
         <v>手机</v>
       </c>
+      <c r="K127" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L127" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -4509,6 +5273,12 @@
       <c r="J128" t="str">
         <v>手机</v>
       </c>
+      <c r="K128" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L128" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -4541,6 +5311,12 @@
       <c r="J129" t="str">
         <v>手机</v>
       </c>
+      <c r="K129" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L129" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -4573,6 +5349,12 @@
       <c r="J130" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K130" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L130" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -4605,6 +5387,12 @@
       <c r="J131" t="str">
         <v>手机</v>
       </c>
+      <c r="K131" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L131" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -4637,6 +5425,12 @@
       <c r="J132" t="str">
         <v>手机</v>
       </c>
+      <c r="K132" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L132" t="str">
+        <v>长沙库</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -4669,6 +5463,12 @@
       <c r="J133" t="str">
         <v>手机</v>
       </c>
+      <c r="K133" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L133" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -4701,6 +5501,12 @@
       <c r="J134" t="str">
         <v>手机</v>
       </c>
+      <c r="K134" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L134" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -4733,6 +5539,12 @@
       <c r="J135" t="str">
         <v>手机</v>
       </c>
+      <c r="K135" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L135" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -4765,6 +5577,12 @@
       <c r="J136" t="str">
         <v>手机</v>
       </c>
+      <c r="K136" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L136" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -4797,6 +5615,12 @@
       <c r="J137" t="str">
         <v>手机</v>
       </c>
+      <c r="K137" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L137" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -4829,6 +5653,12 @@
       <c r="J138" t="str">
         <v>手机</v>
       </c>
+      <c r="K138" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L138" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -4861,6 +5691,12 @@
       <c r="J139" t="str">
         <v>手机</v>
       </c>
+      <c r="K139" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L139" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -4893,6 +5729,12 @@
       <c r="J140" t="str">
         <v>智能手表</v>
       </c>
+      <c r="K140" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L140" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -4925,6 +5767,12 @@
       <c r="J141" t="str">
         <v>手机</v>
       </c>
+      <c r="K141" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L141" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -4957,6 +5805,12 @@
       <c r="J142" t="str">
         <v>手机</v>
       </c>
+      <c r="K142" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L142" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="143" xml:space="preserve">
       <c r="A143" t="str">
@@ -4990,6 +5844,12 @@
       <c r="J143" t="str">
         <v>手机</v>
       </c>
+      <c r="K143" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L143" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -5022,6 +5882,12 @@
       <c r="J144" t="str">
         <v>手机</v>
       </c>
+      <c r="K144" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L144" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -5054,6 +5920,12 @@
       <c r="J145" t="str">
         <v>手机</v>
       </c>
+      <c r="K145" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L145" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -5086,6 +5958,12 @@
       <c r="J146" t="str">
         <v>手机</v>
       </c>
+      <c r="K146" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L146" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -5118,6 +5996,12 @@
       <c r="J147" t="str">
         <v>手机</v>
       </c>
+      <c r="K147" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L147" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -5150,6 +6034,12 @@
       <c r="J148" t="str">
         <v>手机</v>
       </c>
+      <c r="K148" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L148" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -5182,6 +6072,12 @@
       <c r="J149" t="str">
         <v>手机</v>
       </c>
+      <c r="K149" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L149" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -5214,6 +6110,12 @@
       <c r="J150" t="str">
         <v>手机</v>
       </c>
+      <c r="K150" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L150" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -5246,6 +6148,12 @@
       <c r="J151" t="str">
         <v>手机</v>
       </c>
+      <c r="K151" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L151" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -5278,6 +6186,12 @@
       <c r="J152" t="str">
         <v>手机</v>
       </c>
+      <c r="K152" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L152" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -5310,6 +6224,12 @@
       <c r="J153" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K153" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L153" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -5342,6 +6262,12 @@
       <c r="J154" t="str">
         <v>手机</v>
       </c>
+      <c r="K154" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L154" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -5374,6 +6300,12 @@
       <c r="J155" t="str">
         <v>手机</v>
       </c>
+      <c r="K155" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L155" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -5406,6 +6338,12 @@
       <c r="J156" t="str">
         <v>智能手表</v>
       </c>
+      <c r="K156" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L156" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -5438,6 +6376,12 @@
       <c r="J157" t="str">
         <v>手机</v>
       </c>
+      <c r="K157" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L157" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -5470,6 +6414,12 @@
       <c r="J158" t="str">
         <v>手机</v>
       </c>
+      <c r="K158" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L158" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -5502,6 +6452,12 @@
       <c r="J159" t="str">
         <v>手机</v>
       </c>
+      <c r="K159" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L159" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -5534,6 +6490,12 @@
       <c r="J160" t="str">
         <v>手机</v>
       </c>
+      <c r="K160" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L160" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -5566,6 +6528,12 @@
       <c r="J161" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K161" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L161" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -5598,6 +6566,12 @@
       <c r="J162" t="str">
         <v>手机</v>
       </c>
+      <c r="K162" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L162" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -5630,6 +6604,12 @@
       <c r="J163" t="str">
         <v>手机</v>
       </c>
+      <c r="K163" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L163" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -5662,6 +6642,12 @@
       <c r="J164" t="str">
         <v>手机</v>
       </c>
+      <c r="K164" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L164" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -5694,6 +6680,12 @@
       <c r="J165" t="str">
         <v>手机</v>
       </c>
+      <c r="K165" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L165" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -5726,6 +6718,12 @@
       <c r="J166" t="str">
         <v>手机</v>
       </c>
+      <c r="K166" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L166" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -5758,6 +6756,12 @@
       <c r="J167" t="str">
         <v>手机</v>
       </c>
+      <c r="K167" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L167" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -5789,6 +6793,12 @@
       </c>
       <c r="J168" t="str">
         <v>手机</v>
+      </c>
+      <c r="K168" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L168" t="str">
+        <v>重庆库</v>
       </c>
     </row>
     <row r="169" xml:space="preserve">
@@ -5826,6 +6836,12 @@
       <c r="J169" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K169" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L169" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -5858,6 +6874,12 @@
       <c r="J170" t="str">
         <v>手机</v>
       </c>
+      <c r="K170" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L170" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -5890,6 +6912,12 @@
       <c r="J171" t="str">
         <v>手机</v>
       </c>
+      <c r="K171" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L171" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -5922,6 +6950,12 @@
       <c r="J172" t="str">
         <v>手机</v>
       </c>
+      <c r="K172" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L172" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -5954,6 +6988,12 @@
       <c r="J173" t="str">
         <v>手机</v>
       </c>
+      <c r="K173" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L173" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -5986,6 +7026,12 @@
       <c r="J174" t="str">
         <v>手机</v>
       </c>
+      <c r="K174" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L174" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -6018,6 +7064,12 @@
       <c r="J175" t="str">
         <v>手机</v>
       </c>
+      <c r="K175" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L175" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -6050,6 +7102,12 @@
       <c r="J176" t="str">
         <v>手机</v>
       </c>
+      <c r="K176" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L176" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -6082,6 +7140,12 @@
       <c r="J177" t="str">
         <v>智能手表</v>
       </c>
+      <c r="K177" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L177" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -6114,6 +7178,12 @@
       <c r="J178" t="str">
         <v>手机</v>
       </c>
+      <c r="K178" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L178" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -6146,6 +7216,12 @@
       <c r="J179" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K179" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L179" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -6178,6 +7254,12 @@
       <c r="J180" t="str">
         <v>手机</v>
       </c>
+      <c r="K180" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L180" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -6210,6 +7292,12 @@
       <c r="J181" t="str">
         <v>手机</v>
       </c>
+      <c r="K181" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L181" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -6242,6 +7330,12 @@
       <c r="J182" t="str">
         <v>手机</v>
       </c>
+      <c r="K182" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L182" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -6274,6 +7368,12 @@
       <c r="J183" t="str">
         <v>手机</v>
       </c>
+      <c r="K183" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L183" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -6306,6 +7406,12 @@
       <c r="J184" t="str">
         <v>手机</v>
       </c>
+      <c r="K184" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L184" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -6338,6 +7444,12 @@
       <c r="J185" t="str">
         <v>手机</v>
       </c>
+      <c r="K185" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L185" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -6370,6 +7482,12 @@
       <c r="J186" t="str">
         <v/>
       </c>
+      <c r="K186" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L186" t="str">
+        <v>转转-深圳智能验机中心</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -6402,6 +7520,12 @@
       <c r="J187" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K187" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L187" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="188" xml:space="preserve">
       <c r="A188" t="str">
@@ -6435,6 +7559,12 @@
       <c r="J188" t="str">
         <v>手机</v>
       </c>
+      <c r="K188" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L188" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -6467,6 +7597,12 @@
       <c r="J189" t="str">
         <v>手机</v>
       </c>
+      <c r="K189" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L189" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -6499,6 +7635,12 @@
       <c r="J190" t="str">
         <v>手机</v>
       </c>
+      <c r="K190" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L190" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -6531,6 +7673,12 @@
       <c r="J191" t="str">
         <v>手机</v>
       </c>
+      <c r="K191" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L191" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -6563,6 +7711,12 @@
       <c r="J192" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K192" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L192" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -6595,6 +7749,12 @@
       <c r="J193" t="str">
         <v>手机</v>
       </c>
+      <c r="K193" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L193" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -6627,6 +7787,12 @@
       <c r="J194" t="str">
         <v>手机</v>
       </c>
+      <c r="K194" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L194" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -6658,6 +7824,12 @@
       </c>
       <c r="J195" t="str">
         <v>手机</v>
+      </c>
+      <c r="K195" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L195" t="str">
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="196" xml:space="preserve">
@@ -6694,6 +7866,12 @@
       <c r="J196" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K196" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L196" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -6726,6 +7904,12 @@
       <c r="J197" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K197" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L197" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -6758,6 +7942,12 @@
       <c r="J198" t="str">
         <v>手机</v>
       </c>
+      <c r="K198" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L198" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -6790,6 +7980,12 @@
       <c r="J199" t="str">
         <v>手机</v>
       </c>
+      <c r="K199" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L199" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -6822,6 +8018,12 @@
       <c r="J200" t="str">
         <v>手机</v>
       </c>
+      <c r="K200" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L200" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -6854,6 +8056,12 @@
       <c r="J201" t="str">
         <v>手机</v>
       </c>
+      <c r="K201" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L201" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -6886,6 +8094,12 @@
       <c r="J202" t="str">
         <v>手机</v>
       </c>
+      <c r="K202" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L202" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -6918,6 +8132,12 @@
       <c r="J203" t="str">
         <v>手机</v>
       </c>
+      <c r="K203" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L203" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -6950,6 +8170,12 @@
       <c r="J204" t="str">
         <v>手机</v>
       </c>
+      <c r="K204" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L204" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -6982,6 +8208,12 @@
       <c r="J205" t="str">
         <v>手机</v>
       </c>
+      <c r="K205" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L205" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -7014,6 +8246,12 @@
       <c r="J206" t="str">
         <v>单电/微单套机</v>
       </c>
+      <c r="K206" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L206" t="str">
+        <v>转转-深圳智能验机中心</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -7045,6 +8283,12 @@
       </c>
       <c r="J207" t="str">
         <v>平板电脑</v>
+      </c>
+      <c r="K207" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L207" t="str">
+        <v>南京库</v>
       </c>
     </row>
     <row r="208" xml:space="preserve">
@@ -7080,6 +8324,12 @@
       <c r="J208" t="str">
         <v>手机</v>
       </c>
+      <c r="K208" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L208" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -7112,6 +8362,12 @@
       <c r="J209" t="str">
         <v>手机</v>
       </c>
+      <c r="K209" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L209" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -7144,6 +8400,12 @@
       <c r="J210" t="str">
         <v>手机</v>
       </c>
+      <c r="K210" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L210" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -7176,6 +8438,12 @@
       <c r="J211" t="str">
         <v>手机</v>
       </c>
+      <c r="K211" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L211" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -7208,6 +8476,12 @@
       <c r="J212" t="str">
         <v>手机</v>
       </c>
+      <c r="K212" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L212" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -7240,6 +8514,12 @@
       <c r="J213" t="str">
         <v>手机</v>
       </c>
+      <c r="K213" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L213" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -7272,6 +8552,12 @@
       <c r="J214" t="str">
         <v>手机</v>
       </c>
+      <c r="K214" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L214" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -7304,6 +8590,12 @@
       <c r="J215" t="str">
         <v>手机</v>
       </c>
+      <c r="K215" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L215" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -7336,6 +8628,12 @@
       <c r="J216" t="str">
         <v>手机</v>
       </c>
+      <c r="K216" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L216" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -7368,6 +8666,12 @@
       <c r="J217" t="str">
         <v>手机</v>
       </c>
+      <c r="K217" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L217" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -7400,6 +8704,12 @@
       <c r="J218" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K218" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L218" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -7432,6 +8742,12 @@
       <c r="J219" t="str">
         <v>平板电脑</v>
       </c>
+      <c r="K219" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L219" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -7464,6 +8780,12 @@
       <c r="J220" t="str">
         <v>手机</v>
       </c>
+      <c r="K220" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L220" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -7496,6 +8818,12 @@
       <c r="J221" t="str">
         <v>手机</v>
       </c>
+      <c r="K221" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L221" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -7528,6 +8856,12 @@
       <c r="J222" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K222" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L222" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -7560,6 +8894,12 @@
       <c r="J223" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K223" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L223" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -7592,6 +8932,12 @@
       <c r="J224" t="str">
         <v>手机</v>
       </c>
+      <c r="K224" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L224" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -7624,6 +8970,12 @@
       <c r="J225" t="str">
         <v>手机</v>
       </c>
+      <c r="K225" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L225" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -7656,6 +9008,12 @@
       <c r="J226" t="str">
         <v>笔记本</v>
       </c>
+      <c r="K226" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L226" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -7688,6 +9046,12 @@
       <c r="J227" t="str">
         <v>手机</v>
       </c>
+      <c r="K227" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L227" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -7720,6 +9084,12 @@
       <c r="J228" t="str">
         <v>手机</v>
       </c>
+      <c r="K228" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L228" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -7752,6 +9122,12 @@
       <c r="J229" t="str">
         <v>手机</v>
       </c>
+      <c r="K229" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L229" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -7783,6 +9159,12 @@
       </c>
       <c r="J230" t="str">
         <v>手机</v>
+      </c>
+      <c r="K230" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L230" t="str">
+        <v>郑州库</v>
       </c>
     </row>
     <row r="231" xml:space="preserve">
@@ -7821,6 +9203,12 @@
       <c r="J231" t="str">
         <v>手机</v>
       </c>
+      <c r="K231" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L231" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -7853,6 +9241,12 @@
       <c r="J232" t="str">
         <v>手机</v>
       </c>
+      <c r="K232" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L232" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -7885,6 +9279,12 @@
       <c r="J233" t="str">
         <v>手机</v>
       </c>
+      <c r="K233" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L233" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -7917,6 +9317,12 @@
       <c r="J234" t="str">
         <v>手机</v>
       </c>
+      <c r="K234" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L234" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="235" xml:space="preserve">
       <c r="A235" t="str">
@@ -7950,6 +9356,12 @@
       <c r="J235" t="str">
         <v>手机</v>
       </c>
+      <c r="K235" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L235" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -7982,6 +9394,12 @@
       <c r="J236" t="str">
         <v>手机</v>
       </c>
+      <c r="K236" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L236" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -8014,6 +9432,12 @@
       <c r="J237" t="str">
         <v>手机</v>
       </c>
+      <c r="K237" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L237" t="str">
+        <v>廊坊-于释尧（已验机2.0）</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -8046,10 +9470,16 @@
       <c r="J238" t="str">
         <v>手机</v>
       </c>
+      <c r="K238" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="L238" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J238"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L238"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/feedback-daily.xlsx
+++ b/feedback-daily.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L499"/>
+  <dimension ref="A1:N499"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,6 +436,12 @@
       <c r="L1" t="str">
         <v>中心仓</v>
       </c>
+      <c r="M1" t="str">
+        <v>业务线</v>
+      </c>
+      <c r="N1" t="str">
+        <v>中心仓</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -474,6 +480,12 @@
       <c r="L2" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M2" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N2" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -512,6 +524,12 @@
       <c r="L3" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M3" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N3" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -550,6 +568,12 @@
       <c r="L4" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M4" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N4" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -588,6 +612,12 @@
       <c r="L5" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M5" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N5" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -626,6 +656,12 @@
       <c r="L6" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M6" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N6" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -664,6 +700,12 @@
       <c r="L7" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M7" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N7" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -702,6 +744,12 @@
       <c r="L8" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M8" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N8" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -740,6 +788,12 @@
       <c r="L9" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M9" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N9" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -778,6 +832,12 @@
       <c r="L10" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M10" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N10" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -816,6 +876,12 @@
       <c r="L11" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M11" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N11" t="str">
+        <v>洛阳-李鹏远（已验机plus）</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -854,6 +920,12 @@
       <c r="L12" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M12" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N12" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -892,6 +964,12 @@
       <c r="L13" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M13" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N13" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -930,6 +1008,12 @@
       <c r="L14" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M14" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N14" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -968,6 +1052,12 @@
       <c r="L15" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M15" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N15" t="str">
+        <v>成都-王庭益（已验机2.0）</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1006,6 +1096,12 @@
       <c r="L16" t="str">
         <v>济南库</v>
       </c>
+      <c r="M16" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N16" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1044,6 +1140,12 @@
       <c r="L17" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M17" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N17" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1082,6 +1184,12 @@
       <c r="L18" t="str">
         <v>展示机</v>
       </c>
+      <c r="M18" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N18" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1120,6 +1228,12 @@
       <c r="L19" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M19" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N19" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1158,6 +1272,12 @@
       <c r="L20" t="str">
         <v>长沙库</v>
       </c>
+      <c r="M20" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N20" t="str">
+        <v>长沙库</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1196,6 +1316,12 @@
       <c r="L21" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M21" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N21" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1234,6 +1360,12 @@
       <c r="L22" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M22" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N22" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1272,6 +1404,12 @@
       <c r="L23" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M23" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N23" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1310,6 +1448,12 @@
       <c r="L24" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M24" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N24" t="str">
+        <v>深圳-迟恭彦（自质检2.0）</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1348,6 +1492,12 @@
       <c r="L25" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M25" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N25" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1386,6 +1536,12 @@
       <c r="L26" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M26" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N26" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1424,6 +1580,12 @@
       <c r="L27" t="str">
         <v>济南库</v>
       </c>
+      <c r="M27" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N27" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1462,6 +1624,12 @@
       <c r="L28" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M28" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N28" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1500,6 +1668,12 @@
       <c r="L29" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M29" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N29" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1538,6 +1712,12 @@
       <c r="L30" t="str">
         <v>成都库</v>
       </c>
+      <c r="M30" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N30" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1576,6 +1756,12 @@
       <c r="L31" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M31" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N31" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1614,6 +1800,12 @@
       <c r="L32" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M32" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N32" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1652,6 +1844,12 @@
       <c r="L33" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M33" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N33" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1690,6 +1888,12 @@
       <c r="L34" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M34" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N34" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1728,6 +1932,12 @@
       <c r="L35" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M35" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N35" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1766,6 +1976,12 @@
       <c r="L36" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M36" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N36" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1804,6 +2020,12 @@
       <c r="L37" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M37" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N37" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1842,6 +2064,12 @@
       <c r="L38" t="str">
         <v>南昌库</v>
       </c>
+      <c r="M38" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N38" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1880,6 +2108,12 @@
       <c r="L39" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M39" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N39" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1918,6 +2152,12 @@
       <c r="L40" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M40" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N40" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1956,6 +2196,12 @@
       <c r="L41" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M41" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N41" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1994,6 +2240,12 @@
       <c r="L42" t="str">
         <v>济南库</v>
       </c>
+      <c r="M42" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N42" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2032,6 +2284,12 @@
       <c r="L43" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M43" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N43" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2070,6 +2328,12 @@
       <c r="L44" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M44" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N44" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2108,6 +2372,12 @@
       <c r="L45" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M45" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N45" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2146,6 +2416,12 @@
       <c r="L46" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M46" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N46" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2184,6 +2460,12 @@
       <c r="L47" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M47" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N47" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2222,6 +2504,12 @@
       <c r="L48" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M48" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N48" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2260,6 +2548,12 @@
       <c r="L49" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M49" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N49" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2298,6 +2592,12 @@
       <c r="L50" t="str">
         <v/>
       </c>
+      <c r="M50" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N50" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2336,6 +2636,12 @@
       <c r="L51" t="str">
         <v>深圳中心仓</v>
       </c>
+      <c r="M51" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N51" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2374,6 +2680,12 @@
       <c r="L52" t="str">
         <v>BS机</v>
       </c>
+      <c r="M52" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N52" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2412,6 +2724,12 @@
       <c r="L53" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M53" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N53" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2450,6 +2768,12 @@
       <c r="L54" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M54" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N54" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2488,6 +2812,12 @@
       <c r="L55" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M55" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N55" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2526,6 +2856,12 @@
       <c r="L56" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M56" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N56" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2564,6 +2900,12 @@
       <c r="L57" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M57" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N57" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2602,6 +2944,12 @@
       <c r="L58" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M58" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N58" t="str">
+        <v>深圳-迟恭彦（自质检2.0）</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2640,6 +2988,12 @@
       <c r="L59" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M59" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N59" t="str">
+        <v>深圳-迟恭彦（自质检2.0）</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2678,6 +3032,12 @@
       <c r="L60" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M60" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N60" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2716,6 +3076,12 @@
       <c r="L61" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M61" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N61" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2754,6 +3120,12 @@
       <c r="L62" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M62" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N62" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2792,6 +3164,12 @@
       <c r="L63" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M63" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N63" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2830,6 +3208,12 @@
       <c r="L64" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M64" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N64" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2868,6 +3252,12 @@
       <c r="L65" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M65" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N65" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2906,6 +3296,12 @@
       <c r="L66" t="str">
         <v/>
       </c>
+      <c r="M66" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N66" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -2944,6 +3340,12 @@
       <c r="L67" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M67" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N67" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -2982,6 +3384,12 @@
       <c r="L68" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M68" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N68" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3020,6 +3428,12 @@
       <c r="L69" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M69" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N69" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3058,6 +3472,12 @@
       <c r="L70" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M70" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N70" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3096,6 +3516,12 @@
       <c r="L71" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M71" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N71" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3134,6 +3560,12 @@
       <c r="L72" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M72" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N72" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -3172,6 +3604,12 @@
       <c r="L73" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M73" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N73" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -3210,6 +3648,12 @@
       <c r="L74" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M74" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N74" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -3248,6 +3692,12 @@
       <c r="L75" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M75" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N75" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -3286,6 +3736,12 @@
       <c r="L76" t="str">
         <v>展示机</v>
       </c>
+      <c r="M76" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N76" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -3324,6 +3780,12 @@
       <c r="L77" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M77" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N77" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -3362,6 +3824,12 @@
       <c r="L78" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M78" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N78" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -3400,6 +3868,12 @@
       <c r="L79" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M79" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N79" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -3438,6 +3912,12 @@
       <c r="L80" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M80" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N80" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -3476,6 +3956,12 @@
       <c r="L81" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M81" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N81" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -3514,6 +4000,12 @@
       <c r="L82" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M82" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N82" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -3552,6 +4044,12 @@
       <c r="L83" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M83" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N83" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -3590,6 +4088,12 @@
       <c r="L84" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M84" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N84" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -3628,6 +4132,12 @@
       <c r="L85" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M85" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N85" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -3666,6 +4176,12 @@
       <c r="L86" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M86" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N86" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -3704,6 +4220,12 @@
       <c r="L87" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M87" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N87" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -3742,6 +4264,12 @@
       <c r="L88" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M88" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N88" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -3780,6 +4308,12 @@
       <c r="L89" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M89" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N89" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -3818,6 +4352,12 @@
       <c r="L90" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M90" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N90" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -3856,6 +4396,12 @@
       <c r="L91" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M91" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N91" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -3894,6 +4440,12 @@
       <c r="L92" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M92" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N92" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -3932,6 +4484,12 @@
       <c r="L93" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M93" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N93" t="str">
+        <v>福建-魏女（已验机2.0）</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -3970,6 +4528,12 @@
       <c r="L94" t="str">
         <v/>
       </c>
+      <c r="M94" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N94" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4008,6 +4572,12 @@
       <c r="L95" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M95" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N95" t="str">
+        <v>青岛后验中心仓</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4046,6 +4616,12 @@
       <c r="L96" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M96" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N96" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4084,6 +4660,12 @@
       <c r="L97" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M97" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N97" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -4122,6 +4704,12 @@
       <c r="L98" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M98" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N98" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4160,6 +4748,12 @@
       <c r="L99" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M99" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N99" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -4198,6 +4792,12 @@
       <c r="L100" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M100" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N100" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -4236,6 +4836,12 @@
       <c r="L101" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M101" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N101" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -4274,6 +4880,12 @@
       <c r="L102" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M102" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N102" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -4312,6 +4924,12 @@
       <c r="L103" t="str">
         <v/>
       </c>
+      <c r="M103" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N103" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -4350,6 +4968,12 @@
       <c r="L104" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M104" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N104" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -4388,6 +5012,12 @@
       <c r="L105" t="str">
         <v>南昌库</v>
       </c>
+      <c r="M105" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N105" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -4426,6 +5056,12 @@
       <c r="L106" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M106" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N106" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -4464,6 +5100,12 @@
       <c r="L107" t="str">
         <v/>
       </c>
+      <c r="M107" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N107" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="108" xml:space="preserve">
       <c r="A108" t="str">
@@ -4503,6 +5145,12 @@
       <c r="L108" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M108" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N108" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -4541,6 +5189,12 @@
       <c r="L109" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M109" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N109" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="110" xml:space="preserve">
       <c r="A110" t="str">
@@ -4580,6 +5234,12 @@
       <c r="L110" t="str">
         <v>南昌库</v>
       </c>
+      <c r="M110" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N110" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -4618,6 +5278,12 @@
       <c r="L111" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M111" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N111" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -4656,6 +5322,12 @@
       <c r="L112" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M112" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N112" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -4694,6 +5366,12 @@
       <c r="L113" t="str">
         <v>BS机</v>
       </c>
+      <c r="M113" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N113" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4732,6 +5410,12 @@
       <c r="L114" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M114" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N114" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -4770,6 +5454,12 @@
       <c r="L115" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M115" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N115" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -4808,6 +5498,12 @@
       <c r="L116" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M116" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N116" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -4846,6 +5542,12 @@
       <c r="L117" t="str">
         <v/>
       </c>
+      <c r="M117" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N117" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -4884,6 +5586,12 @@
       <c r="L118" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M118" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N118" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -4922,6 +5630,12 @@
       <c r="L119" t="str">
         <v/>
       </c>
+      <c r="M119" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N119" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -4960,6 +5674,12 @@
       <c r="L120" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M120" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N120" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -4998,6 +5718,12 @@
       <c r="L121" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M121" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N121" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -5036,6 +5762,12 @@
       <c r="L122" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M122" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N122" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -5074,6 +5806,12 @@
       <c r="L123" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M123" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N123" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="124" xml:space="preserve">
       <c r="A124" t="str">
@@ -5113,6 +5851,12 @@
       <c r="L124" t="str">
         <v/>
       </c>
+      <c r="M124" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N124" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -5151,6 +5895,12 @@
       <c r="L125" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M125" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N125" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -5189,6 +5939,12 @@
       <c r="L126" t="str">
         <v>展示机</v>
       </c>
+      <c r="M126" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N126" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -5227,6 +5983,12 @@
       <c r="L127" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M127" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N127" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -5265,6 +6027,12 @@
       <c r="L128" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M128" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N128" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -5303,6 +6071,12 @@
       <c r="L129" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M129" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N129" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -5341,6 +6115,12 @@
       <c r="L130" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M130" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N130" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -5379,6 +6159,12 @@
       <c r="L131" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M131" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N131" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -5417,6 +6203,12 @@
       <c r="L132" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M132" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N132" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -5455,6 +6247,12 @@
       <c r="L133" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M133" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N133" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -5493,6 +6291,12 @@
       <c r="L134" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M134" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N134" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -5531,6 +6335,12 @@
       <c r="L135" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M135" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N135" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -5569,6 +6379,12 @@
       <c r="L136" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M136" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N136" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -5607,6 +6423,12 @@
       <c r="L137" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M137" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N137" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -5645,6 +6467,12 @@
       <c r="L138" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M138" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N138" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -5683,6 +6511,12 @@
       <c r="L139" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M139" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N139" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -5721,6 +6555,12 @@
       <c r="L140" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M140" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N140" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -5759,6 +6599,12 @@
       <c r="L141" t="str">
         <v/>
       </c>
+      <c r="M141" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N141" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -5797,6 +6643,12 @@
       <c r="L142" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M142" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N142" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -5835,6 +6687,12 @@
       <c r="L143" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M143" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N143" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -5873,6 +6731,12 @@
       <c r="L144" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M144" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N144" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -5911,6 +6775,12 @@
       <c r="L145" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M145" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N145" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -5949,6 +6819,12 @@
       <c r="L146" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M146" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N146" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -5987,6 +6863,12 @@
       <c r="L147" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M147" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N147" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -6025,6 +6907,12 @@
       <c r="L148" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M148" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N148" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -6063,6 +6951,12 @@
       <c r="L149" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M149" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N149" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -6101,6 +6995,12 @@
       <c r="L150" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M150" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N150" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -6139,6 +7039,12 @@
       <c r="L151" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M151" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N151" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -6177,6 +7083,12 @@
       <c r="L152" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M152" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N152" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -6215,6 +7127,12 @@
       <c r="L153" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M153" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N153" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -6253,6 +7171,12 @@
       <c r="L154" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M154" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N154" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -6291,6 +7215,12 @@
       <c r="L155" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M155" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N155" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -6329,6 +7259,12 @@
       <c r="L156" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M156" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N156" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -6367,6 +7303,12 @@
       <c r="L157" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M157" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N157" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -6405,6 +7347,12 @@
       <c r="L158" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M158" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N158" t="str">
+        <v>长沙库</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -6443,6 +7391,12 @@
       <c r="L159" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M159" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N159" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -6481,6 +7435,12 @@
       <c r="L160" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M160" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N160" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -6519,6 +7479,12 @@
       <c r="L161" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M161" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N161" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -6557,6 +7523,12 @@
       <c r="L162" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M162" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N162" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -6595,6 +7567,12 @@
       <c r="L163" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M163" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N163" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -6633,6 +7611,12 @@
       <c r="L164" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M164" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N164" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -6671,6 +7655,12 @@
       <c r="L165" t="str">
         <v/>
       </c>
+      <c r="M165" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N165" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -6709,6 +7699,12 @@
       <c r="L166" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M166" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N166" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -6747,6 +7743,12 @@
       <c r="L167" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M167" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N167" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -6785,6 +7787,12 @@
       <c r="L168" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M168" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N168" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="169" xml:space="preserve">
       <c r="A169" t="str">
@@ -6824,6 +7832,12 @@
       <c r="L169" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M169" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N169" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -6862,6 +7876,12 @@
       <c r="L170" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M170" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N170" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -6900,6 +7920,12 @@
       <c r="L171" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M171" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N171" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -6938,6 +7964,12 @@
       <c r="L172" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M172" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N172" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -6976,6 +8008,12 @@
       <c r="L173" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M173" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N173" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -7014,6 +8052,12 @@
       <c r="L174" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M174" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N174" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -7052,6 +8096,12 @@
       <c r="L175" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M175" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N175" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -7090,6 +8140,12 @@
       <c r="L176" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M176" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N176" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -7128,6 +8184,12 @@
       <c r="L177" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M177" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N177" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -7166,6 +8228,12 @@
       <c r="L178" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M178" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N178" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -7204,6 +8272,12 @@
       <c r="L179" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M179" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N179" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -7242,6 +8316,12 @@
       <c r="L180" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M180" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N180" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -7280,6 +8360,12 @@
       <c r="L181" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M181" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N181" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -7318,6 +8404,12 @@
       <c r="L182" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M182" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N182" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -7356,6 +8448,12 @@
       <c r="L183" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M183" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N183" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -7394,6 +8492,12 @@
       <c r="L184" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M184" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N184" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -7432,6 +8536,12 @@
       <c r="L185" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M185" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N185" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -7470,6 +8580,12 @@
       <c r="L186" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M186" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N186" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -7508,6 +8624,12 @@
       <c r="L187" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M187" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N187" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -7546,6 +8668,12 @@
       <c r="L188" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M188" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N188" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -7584,6 +8712,12 @@
       <c r="L189" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M189" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N189" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -7622,6 +8756,12 @@
       <c r="L190" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M190" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N190" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -7660,6 +8800,12 @@
       <c r="L191" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M191" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N191" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -7698,6 +8844,12 @@
       <c r="L192" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M192" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N192" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -7736,6 +8888,12 @@
       <c r="L193" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M193" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N193" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -7773,6 +8931,12 @@
       </c>
       <c r="L194" t="str">
         <v>二手优品</v>
+      </c>
+      <c r="M194" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N194" t="str">
+        <v>重庆库</v>
       </c>
     </row>
     <row r="195" xml:space="preserve">
@@ -7816,6 +8980,12 @@
       <c r="L195" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M195" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N195" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -7854,6 +9024,12 @@
       <c r="L196" t="str">
         <v>BS机</v>
       </c>
+      <c r="M196" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N196" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -7892,6 +9068,12 @@
       <c r="L197" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M197" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N197" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -7930,6 +9112,12 @@
       <c r="L198" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M198" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N198" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -7968,6 +9156,12 @@
       <c r="L199" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M199" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N199" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -8006,6 +9200,12 @@
       <c r="L200" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M200" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N200" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -8044,6 +9244,12 @@
       <c r="L201" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M201" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N201" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -8082,6 +9288,12 @@
       <c r="L202" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M202" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N202" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -8120,6 +9332,12 @@
       <c r="L203" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M203" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N203" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -8158,6 +9376,12 @@
       <c r="L204" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M204" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N204" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -8196,6 +9420,12 @@
       <c r="L205" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M205" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N205" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -8234,6 +9464,12 @@
       <c r="L206" t="str">
         <v>深圳中心仓</v>
       </c>
+      <c r="M206" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N206" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -8272,6 +9508,12 @@
       <c r="L207" t="str">
         <v>官翻机</v>
       </c>
+      <c r="M207" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N207" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -8310,6 +9552,12 @@
       <c r="L208" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M208" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N208" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -8348,6 +9596,12 @@
       <c r="L209" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M209" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N209" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -8386,6 +9640,12 @@
       <c r="L210" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M210" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N210" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -8424,6 +9684,12 @@
       <c r="L211" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M211" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N211" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -8462,6 +9728,12 @@
       <c r="L212" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M212" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N212" t="str">
+        <v>转转-深圳智能验机中心</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -8500,6 +9772,12 @@
       <c r="L213" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M213" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N213" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="214" xml:space="preserve">
       <c r="A214" t="str">
@@ -8539,6 +9817,12 @@
       <c r="L214" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M214" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N214" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -8577,6 +9861,12 @@
       <c r="L215" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M215" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N215" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -8615,6 +9905,12 @@
       <c r="L216" t="str">
         <v>郑州库</v>
       </c>
+      <c r="M216" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N216" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -8653,6 +9949,12 @@
       <c r="L217" t="str">
         <v>郑州库</v>
       </c>
+      <c r="M217" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N217" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -8691,6 +9993,12 @@
       <c r="L218" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M218" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N218" t="str">
+        <v>福州库</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -8729,6 +10037,12 @@
       <c r="L219" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M219" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N219" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -8767,6 +10081,12 @@
       <c r="L220" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M220" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N220" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -8804,6 +10124,12 @@
       </c>
       <c r="L221" t="str">
         <v>二手优品</v>
+      </c>
+      <c r="M221" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N221" t="str">
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="222" xml:space="preserve">
@@ -8846,6 +10172,12 @@
       <c r="L222" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M222" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N222" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -8884,6 +10216,12 @@
       <c r="L223" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M223" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N223" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -8922,6 +10260,12 @@
       <c r="L224" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M224" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N224" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -8960,6 +10304,12 @@
       <c r="L225" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M225" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N225" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -8998,6 +10348,12 @@
       <c r="L226" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M226" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N226" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -9036,6 +10392,12 @@
       <c r="L227" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M227" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N227" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -9074,6 +10436,12 @@
       <c r="L228" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M228" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N228" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -9112,6 +10480,12 @@
       <c r="L229" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M229" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N229" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -9150,6 +10524,12 @@
       <c r="L230" t="str">
         <v/>
       </c>
+      <c r="M230" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N230" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -9188,6 +10568,12 @@
       <c r="L231" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M231" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N231" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -9226,6 +10612,12 @@
       <c r="L232" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M232" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N232" t="str">
+        <v>转转-深圳智能验机中心</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -9263,6 +10655,12 @@
       </c>
       <c r="L233" t="str">
         <v>展示机</v>
+      </c>
+      <c r="M233" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N233" t="str">
+        <v>南京库</v>
       </c>
     </row>
     <row r="234" xml:space="preserve">
@@ -9304,6 +10702,12 @@
       <c r="L234" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M234" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N234" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -9342,6 +10746,12 @@
       <c r="L235" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M235" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N235" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -9380,6 +10790,12 @@
       <c r="L236" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M236" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N236" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -9418,6 +10834,12 @@
       <c r="L237" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M237" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N237" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -9456,6 +10878,12 @@
       <c r="L238" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M238" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N238" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -9494,6 +10922,12 @@
       <c r="L239" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M239" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N239" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -9532,6 +10966,12 @@
       <c r="L240" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M240" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N240" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -9570,6 +11010,12 @@
       <c r="L241" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M241" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N241" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -9608,6 +11054,12 @@
       <c r="L242" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M242" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N242" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -9646,6 +11098,12 @@
       <c r="L243" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M243" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N243" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -9684,6 +11142,12 @@
       <c r="L244" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M244" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N244" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -9722,6 +11186,12 @@
       <c r="L245" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M245" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N245" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -9760,6 +11230,12 @@
       <c r="L246" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M246" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N246" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -9798,6 +11274,12 @@
       <c r="L247" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M247" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N247" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -9836,6 +11318,12 @@
       <c r="L248" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M248" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N248" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -9874,6 +11362,12 @@
       <c r="L249" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M249" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N249" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -9912,6 +11406,12 @@
       <c r="L250" t="str">
         <v/>
       </c>
+      <c r="M250" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N250" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -9950,6 +11450,12 @@
       <c r="L251" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M251" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N251" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -9988,6 +11494,12 @@
       <c r="L252" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M252" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N252" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -10026,6 +11538,12 @@
       <c r="L253" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M253" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N253" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -10064,6 +11582,12 @@
       <c r="L254" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M254" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N254" t="str">
+        <v>转转-青岛智能验机中心</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -10102,6 +11626,12 @@
       <c r="L255" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M255" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N255" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -10138,6 +11668,12 @@
         <v/>
       </c>
       <c r="L256" t="str">
+        <v>郑州库</v>
+      </c>
+      <c r="M256" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N256" t="str">
         <v>郑州库</v>
       </c>
     </row>
@@ -10183,6 +11719,12 @@
       <c r="L257" t="str">
         <v/>
       </c>
+      <c r="M257" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N257" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -10221,6 +11763,12 @@
       <c r="L258" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M258" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N258" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -10259,6 +11807,12 @@
       <c r="L259" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M259" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N259" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -10297,6 +11851,12 @@
       <c r="L260" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M260" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N260" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="261" xml:space="preserve">
       <c r="A261" t="str">
@@ -10336,6 +11896,12 @@
       <c r="L261" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M261" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N261" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -10374,6 +11940,12 @@
       <c r="L262" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M262" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N262" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -10412,6 +11984,12 @@
       <c r="L263" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M263" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N263" t="str">
+        <v>廊坊-于释尧（已验机2.0）</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -10450,6 +12028,12 @@
       <c r="L264" t="str">
         <v/>
       </c>
+      <c r="M264" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N264" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -10488,6 +12072,12 @@
       <c r="L265" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M265" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N265" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -10526,6 +12116,12 @@
       <c r="L266" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M266" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N266" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -10564,6 +12160,12 @@
       <c r="L267" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M267" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N267" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -10602,6 +12204,12 @@
       <c r="L268" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M268" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N268" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -10640,6 +12248,12 @@
       <c r="L269" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M269" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N269" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -10678,6 +12292,12 @@
       <c r="L270" t="str">
         <v/>
       </c>
+      <c r="M270" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N270" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -10716,6 +12336,12 @@
       <c r="L271" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M271" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N271" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -10754,6 +12380,12 @@
       <c r="L272" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M272" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N272" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -10792,6 +12424,12 @@
       <c r="L273" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M273" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N273" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -10830,6 +12468,12 @@
       <c r="L274" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M274" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N274" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -10868,6 +12512,12 @@
       <c r="L275" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M275" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N275" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -10906,6 +12556,12 @@
       <c r="L276" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M276" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N276" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -10944,6 +12600,12 @@
       <c r="L277" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M277" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N277" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -10982,6 +12644,12 @@
       <c r="L278" t="str">
         <v/>
       </c>
+      <c r="M278" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N278" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -11020,6 +12688,12 @@
       <c r="L279" t="str">
         <v/>
       </c>
+      <c r="M279" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N279" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -11058,6 +12732,12 @@
       <c r="L280" t="str">
         <v>南昌库</v>
       </c>
+      <c r="M280" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N280" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -11096,6 +12776,12 @@
       <c r="L281" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M281" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N281" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -11134,6 +12820,12 @@
       <c r="L282" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M282" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N282" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -11172,6 +12864,12 @@
       <c r="L283" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M283" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N283" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -11210,6 +12908,12 @@
       <c r="L284" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M284" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N284" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -11248,6 +12952,12 @@
       <c r="L285" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M285" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N285" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -11286,6 +12996,12 @@
       <c r="L286" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M286" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N286" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -11324,6 +13040,12 @@
       <c r="L287" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M287" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N287" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -11362,6 +13084,12 @@
       <c r="L288" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M288" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N288" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -11400,6 +13128,12 @@
       <c r="L289" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M289" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N289" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -11438,6 +13172,12 @@
       <c r="L290" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M290" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N290" t="str">
+        <v>济南-杨帆（多品类）</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -11476,6 +13216,12 @@
       <c r="L291" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M291" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N291" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -11514,6 +13260,12 @@
       <c r="L292" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M292" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N292" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -11552,6 +13304,12 @@
       <c r="L293" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M293" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N293" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -11590,6 +13348,12 @@
       <c r="L294" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M294" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N294" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="295" xml:space="preserve">
       <c r="A295" t="str">
@@ -11629,6 +13393,12 @@
       <c r="L295" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M295" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N295" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -11667,6 +13437,12 @@
       <c r="L296" t="str">
         <v/>
       </c>
+      <c r="M296" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N296" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -11705,6 +13481,12 @@
       <c r="L297" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M297" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N297" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -11743,6 +13525,12 @@
       <c r="L298" t="str">
         <v>官翻机</v>
       </c>
+      <c r="M298" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N298" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -11781,6 +13569,12 @@
       <c r="L299" t="str">
         <v>展示机</v>
       </c>
+      <c r="M299" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N299" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -11819,6 +13613,12 @@
       <c r="L300" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M300" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N300" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -11857,6 +13657,12 @@
       <c r="L301" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M301" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N301" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -11895,6 +13701,12 @@
       <c r="L302" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M302" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N302" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -11933,6 +13745,12 @@
       <c r="L303" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M303" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N303" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -11971,6 +13789,12 @@
       <c r="L304" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M304" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N304" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -12009,6 +13833,12 @@
       <c r="L305" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M305" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N305" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -12047,6 +13877,12 @@
       <c r="L306" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M306" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N306" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -12085,6 +13921,12 @@
       <c r="L307" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M307" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N307" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -12123,6 +13965,12 @@
       <c r="L308" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M308" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N308" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -12161,6 +14009,12 @@
       <c r="L309" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M309" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N309" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -12199,6 +14053,12 @@
       <c r="L310" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M310" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N310" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="311" xml:space="preserve">
       <c r="A311" t="str">
@@ -12238,6 +14098,12 @@
       <c r="L311" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M311" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N311" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -12276,6 +14142,12 @@
       <c r="L312" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M312" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N312" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -12314,6 +14186,12 @@
       <c r="L313" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M313" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N313" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -12352,6 +14230,12 @@
       <c r="L314" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M314" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N314" t="str">
+        <v>沈阳库</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -12390,6 +14274,12 @@
       <c r="L315" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M315" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N315" t="str">
+        <v>武汉库</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -12428,6 +14318,12 @@
       <c r="L316" t="str">
         <v/>
       </c>
+      <c r="M316" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N316" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -12466,6 +14362,12 @@
       <c r="L317" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M317" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N317" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -12504,6 +14406,12 @@
       <c r="L318" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M318" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N318" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -12542,6 +14450,12 @@
       <c r="L319" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M319" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N319" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -12580,6 +14494,12 @@
       <c r="L320" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M320" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N320" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -12618,6 +14538,12 @@
       <c r="L321" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M321" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N321" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -12656,6 +14582,12 @@
       <c r="L322" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M322" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N322" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -12694,6 +14626,12 @@
       <c r="L323" t="str">
         <v/>
       </c>
+      <c r="M323" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N323" t="str">
+        <v>长沙库</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -12732,6 +14670,12 @@
       <c r="L324" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M324" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N324" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -12770,6 +14714,12 @@
       <c r="L325" t="str">
         <v>重庆库</v>
       </c>
+      <c r="M325" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N325" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -12808,6 +14758,12 @@
       <c r="L326" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M326" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N326" t="str">
+        <v>转转-青岛智能验机中心</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -12846,6 +14802,12 @@
       <c r="L327" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M327" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N327" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -12884,6 +14846,12 @@
       <c r="L328" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M328" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N328" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -12922,6 +14890,12 @@
       <c r="L329" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M329" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N329" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -12960,6 +14934,12 @@
       <c r="L330" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M330" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N330" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -12998,6 +14978,12 @@
       <c r="L331" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M331" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N331" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -13036,6 +15022,12 @@
       <c r="L332" t="str">
         <v/>
       </c>
+      <c r="M332" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N332" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -13074,6 +15066,12 @@
       <c r="L333" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M333" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N333" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -13112,6 +15110,12 @@
       <c r="L334" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M334" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N334" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -13150,6 +15154,12 @@
       <c r="L335" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M335" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N335" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -13188,6 +15198,12 @@
       <c r="L336" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M336" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N336" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -13226,6 +15242,12 @@
       <c r="L337" t="str">
         <v/>
       </c>
+      <c r="M337" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N337" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -13264,6 +15286,12 @@
       <c r="L338" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M338" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N338" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -13302,6 +15330,12 @@
       <c r="L339" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M339" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N339" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -13340,6 +15374,12 @@
       <c r="L340" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M340" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N340" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -13378,6 +15418,12 @@
       <c r="L341" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M341" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N341" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -13416,6 +15462,12 @@
       <c r="L342" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M342" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N342" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -13454,6 +15506,12 @@
       <c r="L343" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M343" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N343" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -13492,6 +15550,12 @@
       <c r="L344" t="str">
         <v/>
       </c>
+      <c r="M344" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N344" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -13530,6 +15594,12 @@
       <c r="L345" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M345" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N345" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -13568,6 +15638,12 @@
       <c r="L346" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M346" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N346" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -13606,6 +15682,12 @@
       <c r="L347" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M347" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N347" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -13644,6 +15726,12 @@
       <c r="L348" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M348" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N348" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -13682,6 +15770,12 @@
       <c r="L349" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M349" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N349" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -13720,6 +15814,12 @@
       <c r="L350" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M350" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N350" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -13758,6 +15858,12 @@
       <c r="L351" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M351" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N351" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -13796,6 +15902,12 @@
       <c r="L352" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M352" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N352" t="str">
+        <v>深圳后验中心仓</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -13834,6 +15946,12 @@
       <c r="L353" t="str">
         <v/>
       </c>
+      <c r="M353" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N353" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -13872,6 +15990,12 @@
       <c r="L354" t="str">
         <v>西安库</v>
       </c>
+      <c r="M354" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N354" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -13910,6 +16034,12 @@
       <c r="L355" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M355" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N355" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -13948,6 +16078,12 @@
       <c r="L356" t="str">
         <v>西安库</v>
       </c>
+      <c r="M356" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N356" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -13986,6 +16122,12 @@
       <c r="L357" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M357" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N357" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -14024,6 +16166,12 @@
       <c r="L358" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M358" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N358" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -14062,6 +16210,12 @@
       <c r="L359" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M359" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N359" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -14100,6 +16254,12 @@
       <c r="L360" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M360" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N360" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -14138,6 +16298,12 @@
       <c r="L361" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M361" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N361" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -14176,6 +16342,12 @@
       <c r="L362" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M362" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N362" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -14214,6 +16386,12 @@
       <c r="L363" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M363" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N363" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -14252,6 +16430,12 @@
       <c r="L364" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M364" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N364" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -14290,6 +16474,12 @@
       <c r="L365" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M365" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N365" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -14328,6 +16518,12 @@
       <c r="L366" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M366" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N366" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -14366,6 +16562,12 @@
       <c r="L367" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M367" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N367" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -14404,6 +16606,12 @@
       <c r="L368" t="str">
         <v/>
       </c>
+      <c r="M368" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N368" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -14442,6 +16650,12 @@
       <c r="L369" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M369" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N369" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -14480,6 +16694,12 @@
       <c r="L370" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M370" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N370" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -14518,6 +16738,12 @@
       <c r="L371" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M371" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N371" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -14556,6 +16782,12 @@
       <c r="L372" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M372" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N372" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -14594,6 +16826,12 @@
       <c r="L373" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M373" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N373" t="str">
+        <v>长沙库</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -14632,6 +16870,12 @@
       <c r="L374" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M374" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N374" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -14670,6 +16914,12 @@
       <c r="L375" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M375" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N375" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -14708,6 +16958,12 @@
       <c r="L376" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M376" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N376" t="str">
+        <v>转转-青岛智能验机中心</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -14746,6 +17002,12 @@
       <c r="L377" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M377" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N377" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -14784,6 +17046,12 @@
       <c r="L378" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M378" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N378" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -14822,6 +17090,12 @@
       <c r="L379" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M379" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N379" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -14860,6 +17134,12 @@
       <c r="L380" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M380" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N380" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -14898,6 +17178,12 @@
       <c r="L381" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M381" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N381" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="382" xml:space="preserve">
       <c r="A382" t="str">
@@ -14937,6 +17223,12 @@
       <c r="L382" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M382" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N382" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -14975,6 +17267,12 @@
       <c r="L383" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M383" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N383" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -15013,6 +17311,12 @@
       <c r="L384" t="str">
         <v/>
       </c>
+      <c r="M384" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N384" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -15051,6 +17355,12 @@
       <c r="L385" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M385" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N385" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -15089,6 +17399,12 @@
       <c r="L386" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M386" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N386" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -15127,6 +17443,12 @@
       <c r="L387" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M387" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N387" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -15165,6 +17487,12 @@
       <c r="L388" t="str">
         <v>重庆库</v>
       </c>
+      <c r="M388" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N388" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -15203,6 +17531,12 @@
       <c r="L389" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M389" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N389" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -15241,6 +17575,12 @@
       <c r="L390" t="str">
         <v/>
       </c>
+      <c r="M390" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N390" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
@@ -15279,6 +17619,12 @@
       <c r="L391" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M391" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N391" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -15317,6 +17663,12 @@
       <c r="L392" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M392" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N392" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -15355,6 +17707,12 @@
       <c r="L393" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M393" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N393" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -15393,6 +17751,12 @@
       <c r="L394" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M394" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N394" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -15431,6 +17795,12 @@
       <c r="L395" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M395" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N395" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -15469,6 +17839,12 @@
       <c r="L396" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M396" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N396" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
@@ -15507,6 +17883,12 @@
       <c r="L397" t="str">
         <v/>
       </c>
+      <c r="M397" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N397" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
@@ -15545,6 +17927,12 @@
       <c r="L398" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M398" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N398" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
@@ -15583,6 +17971,12 @@
       <c r="L399" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M399" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N399" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
@@ -15621,6 +18015,12 @@
       <c r="L400" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M400" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N400" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
@@ -15659,6 +18059,12 @@
       <c r="L401" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M401" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N401" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
@@ -15697,6 +18103,12 @@
       <c r="L402" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M402" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N402" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
@@ -15735,6 +18147,12 @@
       <c r="L403" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M403" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N403" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
@@ -15773,6 +18191,12 @@
       <c r="L404" t="str">
         <v/>
       </c>
+      <c r="M404" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N404" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
@@ -15811,6 +18235,12 @@
       <c r="L405" t="str">
         <v/>
       </c>
+      <c r="M405" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N405" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
@@ -15849,6 +18279,12 @@
       <c r="L406" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M406" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N406" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
@@ -15887,6 +18323,12 @@
       <c r="L407" t="str">
         <v/>
       </c>
+      <c r="M407" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N407" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
@@ -15925,6 +18367,12 @@
       <c r="L408" t="str">
         <v/>
       </c>
+      <c r="M408" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N408" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
@@ -15963,6 +18411,12 @@
       <c r="L409" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M409" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N409" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
@@ -16001,6 +18455,12 @@
       <c r="L410" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M410" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N410" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
@@ -16039,6 +18499,12 @@
       <c r="L411" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M411" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N411" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
@@ -16077,6 +18543,12 @@
       <c r="L412" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M412" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N412" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
@@ -16115,6 +18587,12 @@
       <c r="L413" t="str">
         <v/>
       </c>
+      <c r="M413" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N413" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
@@ -16153,6 +18631,12 @@
       <c r="L414" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M414" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N414" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
@@ -16191,6 +18675,12 @@
       <c r="L415" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M415" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N415" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
@@ -16229,6 +18719,12 @@
       <c r="L416" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M416" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N416" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
@@ -16267,6 +18763,12 @@
       <c r="L417" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M417" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N417" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
@@ -16305,6 +18807,12 @@
       <c r="L418" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M418" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N418" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
@@ -16343,6 +18851,12 @@
       <c r="L419" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M419" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N419" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
@@ -16381,6 +18895,12 @@
       <c r="L420" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M420" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N420" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
@@ -16419,6 +18939,12 @@
       <c r="L421" t="str">
         <v/>
       </c>
+      <c r="M421" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N421" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
@@ -16457,6 +18983,12 @@
       <c r="L422" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M422" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N422" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
@@ -16495,6 +19027,12 @@
       <c r="L423" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M423" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N423" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
@@ -16533,6 +19071,12 @@
       <c r="L424" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M424" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N424" t="str">
+        <v>郑州库</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
@@ -16571,6 +19115,12 @@
       <c r="L425" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M425" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N425" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
@@ -16609,6 +19159,12 @@
       <c r="L426" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M426" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N426" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
@@ -16647,6 +19203,12 @@
       <c r="L427" t="str">
         <v/>
       </c>
+      <c r="M427" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N427" t="str">
+        <v>长沙库</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
@@ -16685,6 +19247,12 @@
       <c r="L428" t="str">
         <v/>
       </c>
+      <c r="M428" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N428" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
@@ -16723,6 +19291,12 @@
       <c r="L429" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M429" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N429" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
@@ -16761,6 +19335,12 @@
       <c r="L430" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M430" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N430" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
@@ -16799,6 +19379,12 @@
       <c r="L431" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M431" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N431" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
@@ -16837,6 +19423,12 @@
       <c r="L432" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M432" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N432" t="str">
+        <v>西安库</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
@@ -16875,6 +19467,12 @@
       <c r="L433" t="str">
         <v/>
       </c>
+      <c r="M433" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N433" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
@@ -16913,6 +19511,12 @@
       <c r="L434" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M434" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N434" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
@@ -16951,6 +19555,12 @@
       <c r="L435" t="str">
         <v>重庆库</v>
       </c>
+      <c r="M435" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N435" t="str">
+        <v>重庆库</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
@@ -16989,6 +19599,12 @@
       <c r="L436" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M436" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N436" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
@@ -17027,6 +19643,12 @@
       <c r="L437" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M437" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N437" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
@@ -17065,6 +19687,12 @@
       <c r="L438" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M438" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N438" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
@@ -17103,6 +19731,12 @@
       <c r="L439" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M439" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N439" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
@@ -17141,6 +19775,12 @@
       <c r="L440" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M440" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N440" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
@@ -17179,6 +19819,12 @@
       <c r="L441" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M441" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N441" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
@@ -17217,6 +19863,12 @@
       <c r="L442" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M442" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N442" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
@@ -17255,6 +19907,12 @@
       <c r="L443" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M443" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N443" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
@@ -17293,6 +19951,12 @@
       <c r="L444" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M444" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N444" t="str">
+        <v>转转-成都智能验机中心</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
@@ -17331,6 +19995,12 @@
       <c r="L445" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M445" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N445" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
@@ -17369,6 +20039,12 @@
       <c r="L446" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M446" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N446" t="str">
+        <v>转转-青岛智能验机中心</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
@@ -17407,6 +20083,12 @@
       <c r="L447" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M447" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N447" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
@@ -17445,6 +20127,12 @@
       <c r="L448" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M448" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N448" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
@@ -17483,6 +20171,12 @@
       <c r="L449" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M449" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N449" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
@@ -17521,6 +20215,12 @@
       <c r="L450" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M450" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N450" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
@@ -17559,6 +20259,12 @@
       <c r="L451" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M451" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N451" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
@@ -17597,6 +20303,12 @@
       <c r="L452" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M452" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N452" t="str">
+        <v>成都库</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
@@ -17635,6 +20347,12 @@
       <c r="L453" t="str">
         <v>长沙库</v>
       </c>
+      <c r="M453" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N453" t="str">
+        <v>长沙库</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
@@ -17673,6 +20391,12 @@
       <c r="L454" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M454" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N454" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
@@ -17711,6 +20435,12 @@
       <c r="L455" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M455" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N455" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
@@ -17749,6 +20479,12 @@
       <c r="L456" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M456" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N456" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
@@ -17787,6 +20523,12 @@
       <c r="L457" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M457" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N457" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
@@ -17825,6 +20567,12 @@
       <c r="L458" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M458" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N458" t="str">
+        <v>南昌库</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
@@ -17863,6 +20611,12 @@
       <c r="L459" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M459" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N459" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
@@ -17901,6 +20655,12 @@
       <c r="L460" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M460" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N460" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
@@ -17939,6 +20699,12 @@
       <c r="L461" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M461" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N461" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
@@ -17977,6 +20743,12 @@
       <c r="L462" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M462" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N462" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
@@ -18015,6 +20787,12 @@
       <c r="L463" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M463" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N463" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
@@ -18053,6 +20831,12 @@
       <c r="L464" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M464" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N464" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
@@ -18091,6 +20875,12 @@
       <c r="L465" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M465" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N465" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
@@ -18129,6 +20919,12 @@
       <c r="L466" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M466" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N466" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
@@ -18167,6 +20963,12 @@
       <c r="L467" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M467" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N467" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
@@ -18205,6 +21007,12 @@
       <c r="L468" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M468" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N468" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
@@ -18243,6 +21051,12 @@
       <c r="L469" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M469" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N469" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
@@ -18281,6 +21095,12 @@
       <c r="L470" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M470" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N470" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
@@ -18319,6 +21139,12 @@
       <c r="L471" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M471" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N471" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
@@ -18357,6 +21183,12 @@
       <c r="L472" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M472" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N472" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
@@ -18395,6 +21227,12 @@
       <c r="L473" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M473" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N473" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
@@ -18433,6 +21271,12 @@
       <c r="L474" t="str">
         <v/>
       </c>
+      <c r="M474" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N474" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
@@ -18471,6 +21315,12 @@
       <c r="L475" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M475" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N475" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
@@ -18509,6 +21359,12 @@
       <c r="L476" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M476" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N476" t="str">
+        <v>杭州库</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
@@ -18547,6 +21403,12 @@
       <c r="L477" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M477" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N477" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
@@ -18585,6 +21447,12 @@
       <c r="L478" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M478" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N478" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
@@ -18623,6 +21491,12 @@
       <c r="L479" t="str">
         <v>BS机</v>
       </c>
+      <c r="M479" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N479" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
@@ -18661,6 +21535,12 @@
       <c r="L480" t="str">
         <v>深圳中心仓</v>
       </c>
+      <c r="M480" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N480" t="str">
+        <v>深圳中心仓</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
@@ -18699,6 +21579,12 @@
       <c r="L481" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M481" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N481" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
@@ -18737,6 +21623,12 @@
       <c r="L482" t="str">
         <v>昆明库</v>
       </c>
+      <c r="M482" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N482" t="str">
+        <v>昆明库</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
@@ -18775,6 +21667,12 @@
       <c r="L483" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M483" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N483" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
@@ -18813,6 +21711,12 @@
       <c r="L484" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M484" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N484" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
@@ -18851,6 +21755,12 @@
       <c r="L485" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M485" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N485" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
@@ -18889,6 +21799,12 @@
       <c r="L486" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M486" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N486" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
@@ -18927,6 +21843,12 @@
       <c r="L487" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M487" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N487" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
@@ -18965,6 +21887,12 @@
       <c r="L488" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M488" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N488" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
@@ -19003,6 +21931,12 @@
       <c r="L489" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M489" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N489" t="str">
+        <v>转转-深圳智能验机中心</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
@@ -19041,6 +21975,12 @@
       <c r="L490" t="str">
         <v>BS机</v>
       </c>
+      <c r="M490" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N490" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
@@ -19079,6 +22019,12 @@
       <c r="L491" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M491" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N491" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
@@ -19117,6 +22063,12 @@
       <c r="L492" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M492" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N492" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
@@ -19154,6 +22106,12 @@
       </c>
       <c r="L493" t="str">
         <v>二手优品</v>
+      </c>
+      <c r="M493" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N493" t="str">
+        <v>合肥库</v>
       </c>
     </row>
     <row r="494" xml:space="preserve">
@@ -19196,6 +22154,12 @@
       <c r="L494" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M494" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N494" t="str">
+        <v>合肥库</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
@@ -19234,6 +22198,12 @@
       <c r="L495" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M495" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N495" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
@@ -19272,6 +22242,12 @@
       <c r="L496" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M496" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N496" t="str">
+        <v>济南库</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
@@ -19310,6 +22286,12 @@
       <c r="L497" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M497" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N497" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
@@ -19348,6 +22330,12 @@
       <c r="L498" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M498" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N498" t="str">
+        <v>南京库</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
@@ -19386,10 +22374,16 @@
       <c r="L499" t="str">
         <v>二手优品</v>
       </c>
+      <c r="M499" t="str">
+        <v>入仓质检</v>
+      </c>
+      <c r="N499" t="str">
+        <v>石家庄库</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L499"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N499"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/feedback-daily.xlsx
+++ b/feedback-daily.xlsx
@@ -1413,7 +1413,7 @@
         <v>这不就是是很细小的细磨吗</v>
       </c>
       <c r="I27" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J27" t="str">
         <v>手机</v>
@@ -1451,7 +1451,7 @@
         <v>这不是轻微吧，正常都是上99的</v>
       </c>
       <c r="I28" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J28" t="str">
         <v>手机</v>

--- a/feedback-daily.xlsx
+++ b/feedback-daily.xlsx
@@ -807,7 +807,7 @@
         <v>不认可</v>
       </c>
       <c r="I11" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J11" t="str">
         <v>手机</v>
@@ -1835,7 +1835,7 @@
         <v/>
       </c>
       <c r="I38" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J38" t="str">
         <v>手机</v>

--- a/feedback-daily.xlsx
+++ b/feedback-daily.xlsx
@@ -469,10 +469,10 @@
         <v>手机</v>
       </c>
       <c r="K2" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>郑州中心仓</v>
       </c>
     </row>
     <row r="3">
@@ -507,10 +507,10 @@
         <v>笔记本</v>
       </c>
       <c r="K3" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>笔记本</v>
       </c>
       <c r="K4" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="5">
@@ -583,10 +583,10 @@
         <v>笔记本</v>
       </c>
       <c r="K5" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="6">
@@ -621,10 +621,10 @@
         <v>笔记本</v>
       </c>
       <c r="K6" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="7">
@@ -659,10 +659,10 @@
         <v>笔记本</v>
       </c>
       <c r="K7" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="8">
@@ -697,10 +697,10 @@
         <v>笔记本</v>
       </c>
       <c r="K8" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="9">
@@ -735,10 +735,10 @@
         <v>手机</v>
       </c>
       <c r="K9" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="10">
@@ -773,10 +773,10 @@
         <v>手机</v>
       </c>
       <c r="K10" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="11">
@@ -811,7 +811,7 @@
         <v>手机</v>
       </c>
       <c r="K11" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -849,7 +849,7 @@
         <v>手机</v>
       </c>
       <c r="K12" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L12" t="str">
         <v>南京中心仓</v>
@@ -887,7 +887,7 @@
         <v>手机</v>
       </c>
       <c r="K13" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L13" t="str">
         <v>青岛中心仓</v>
@@ -925,7 +925,7 @@
         <v>手机</v>
       </c>
       <c r="K14" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L14" t="str">
         <v>合肥中心仓</v>
@@ -963,10 +963,10 @@
         <v>笔记本</v>
       </c>
       <c r="K15" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>郑州中心仓</v>
       </c>
     </row>
     <row r="16">
@@ -1001,10 +1001,10 @@
         <v>手机</v>
       </c>
       <c r="K16" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>重庆中心仓</v>
       </c>
     </row>
     <row r="17">
@@ -1039,10 +1039,10 @@
         <v>手机</v>
       </c>
       <c r="K17" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>重庆中心仓</v>
       </c>
     </row>
     <row r="18">
@@ -1077,10 +1077,10 @@
         <v>手机</v>
       </c>
       <c r="K18" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>重庆中心仓</v>
       </c>
     </row>
     <row r="19">
@@ -1115,10 +1115,10 @@
         <v>手机</v>
       </c>
       <c r="K19" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>重庆中心仓</v>
       </c>
     </row>
     <row r="20">
@@ -1153,10 +1153,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K20" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="21">
@@ -1191,7 +1191,7 @@
         <v>手机</v>
       </c>
       <c r="K21" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L21" t="str">
         <v>南京中心仓</v>
@@ -1229,10 +1229,10 @@
         <v>笔记本</v>
       </c>
       <c r="K22" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>郑州中心仓</v>
       </c>
     </row>
     <row r="23">
@@ -1267,7 +1267,7 @@
         <v>笔记本</v>
       </c>
       <c r="K23" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L23" t="str">
         <v>武汉中心仓</v>
@@ -1305,7 +1305,7 @@
         <v>笔记本</v>
       </c>
       <c r="K24" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L24" t="str">
         <v>武汉中心仓</v>
@@ -1343,10 +1343,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K25" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="26">
@@ -1381,10 +1381,10 @@
         <v>手机</v>
       </c>
       <c r="K26" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="27">
@@ -1419,7 +1419,7 @@
         <v>手机</v>
       </c>
       <c r="K27" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L27" t="str">
         <v>南京中心仓</v>
@@ -1457,10 +1457,10 @@
         <v>手机</v>
       </c>
       <c r="K28" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="29">
@@ -1495,10 +1495,10 @@
         <v>手机</v>
       </c>
       <c r="K29" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="30">
@@ -1533,10 +1533,10 @@
         <v>手机</v>
       </c>
       <c r="K30" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="31">
@@ -1571,10 +1571,10 @@
         <v>手机</v>
       </c>
       <c r="K31" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="32">
@@ -1609,10 +1609,10 @@
         <v>手机</v>
       </c>
       <c r="K32" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="33">
@@ -1647,10 +1647,10 @@
         <v>手机</v>
       </c>
       <c r="K33" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L33" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="34">
@@ -1685,10 +1685,10 @@
         <v>手机</v>
       </c>
       <c r="K34" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L34" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="35">
@@ -1723,7 +1723,7 @@
         <v>手机</v>
       </c>
       <c r="K35" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L35" t="str">
         <v>杭州中心仓</v>
@@ -1761,7 +1761,7 @@
         <v>手机</v>
       </c>
       <c r="K36" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L36" t="str">
         <v>成都中心仓</v>
@@ -1793,13 +1793,13 @@
         <v>好的机器，没问题的</v>
       </c>
       <c r="I37" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J37" t="str">
         <v>手机</v>
       </c>
       <c r="K37" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L37" t="str">
         <v>南京中心仓</v>
@@ -1837,7 +1837,7 @@
         <v>笔记本</v>
       </c>
       <c r="K38" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L38" t="str">
         <v>上海中心仓</v>
@@ -1875,7 +1875,7 @@
         <v>手机</v>
       </c>
       <c r="K39" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L39" t="str">
         <v>南京中心仓</v>
@@ -1907,16 +1907,16 @@
         <v xml:space="preserve">没那么严重啊 </v>
       </c>
       <c r="I40" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J40" t="str">
         <v>手机</v>
       </c>
       <c r="K40" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L40" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="41">
@@ -1951,7 +1951,7 @@
         <v>笔记本</v>
       </c>
       <c r="K41" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L41" t="str">
         <v>广州中心仓</v>
@@ -1989,10 +1989,10 @@
         <v>手机</v>
       </c>
       <c r="K42" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L42" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="43">
@@ -2027,10 +2027,10 @@
         <v>手机</v>
       </c>
       <c r="K43" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L43" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="44">
@@ -2065,10 +2065,10 @@
         <v>手机</v>
       </c>
       <c r="K44" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L44" t="str">
-        <v/>
+        <v>昆明中心仓</v>
       </c>
     </row>
     <row r="45">
@@ -2103,7 +2103,7 @@
         <v>手机</v>
       </c>
       <c r="K45" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L45" t="str">
         <v>深圳中心仓</v>
@@ -2141,7 +2141,7 @@
         <v>手机</v>
       </c>
       <c r="K46" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L46" t="str">
         <v>南京中心仓</v>
@@ -2179,10 +2179,10 @@
         <v>手机</v>
       </c>
       <c r="K47" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L47" t="str">
-        <v/>
+        <v>昆明中心仓</v>
       </c>
     </row>
     <row r="48">
@@ -2211,13 +2211,13 @@
         <v>不存在外屏更换，可以去售后检测的，这个机器我这小哥自己用的，麻烦大哥再看看哈，感谢</v>
       </c>
       <c r="I48" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J48" t="str">
         <v>手机</v>
       </c>
       <c r="K48" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L48" t="str">
         <v>南京中心仓</v>
@@ -2255,7 +2255,7 @@
         <v>笔记本</v>
       </c>
       <c r="K49" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L49" t="str">
         <v>成都中心仓</v>
@@ -2293,7 +2293,7 @@
         <v>笔记本</v>
       </c>
       <c r="K50" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L50" t="str">
         <v>郑州中心仓</v>
@@ -2331,10 +2331,10 @@
         <v>手机</v>
       </c>
       <c r="K51" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L51" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="52">
@@ -2369,7 +2369,7 @@
         <v>手机</v>
       </c>
       <c r="K52" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L52" t="str">
         <v>成都中心仓</v>
@@ -2407,10 +2407,10 @@
         <v>手机</v>
       </c>
       <c r="K53" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L53" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="54">
@@ -2445,10 +2445,10 @@
         <v>手机</v>
       </c>
       <c r="K54" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L54" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="55">
@@ -2483,7 +2483,7 @@
         <v>手机</v>
       </c>
       <c r="K55" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L55" t="str">
         <v>沈阳中心仓</v>
@@ -2521,7 +2521,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K56" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L56" t="str">
         <v>石家庄中心仓</v>
@@ -2559,7 +2559,7 @@
         <v>手机</v>
       </c>
       <c r="K57" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L57" t="str">
         <v>济南中心仓</v>
@@ -2600,7 +2600,7 @@
         <v>耳机/耳麦</v>
       </c>
       <c r="K58" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L58" t="str">
         <v>杭州中心仓</v>
@@ -2638,7 +2638,7 @@
         <v>手机</v>
       </c>
       <c r="K59" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L59" t="str">
         <v>南京中心仓</v>
@@ -2676,7 +2676,7 @@
         <v>手机</v>
       </c>
       <c r="K60" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L60" t="str">
         <v>南京中心仓</v>
@@ -2714,7 +2714,7 @@
         <v>手机</v>
       </c>
       <c r="K61" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L61" t="str">
         <v>郑州中心仓</v>
@@ -2752,10 +2752,10 @@
         <v>手机</v>
       </c>
       <c r="K62" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L62" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="63">
@@ -2790,10 +2790,10 @@
         <v>手机</v>
       </c>
       <c r="K63" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L63" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="64">
@@ -2828,10 +2828,10 @@
         <v>手机</v>
       </c>
       <c r="K64" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L64" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="65">
@@ -2866,10 +2866,10 @@
         <v>手机</v>
       </c>
       <c r="K65" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L65" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="66">
@@ -2904,10 +2904,10 @@
         <v>手机</v>
       </c>
       <c r="K66" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L66" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="67">
@@ -2942,10 +2942,10 @@
         <v>手机</v>
       </c>
       <c r="K67" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L67" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="68">
@@ -2980,10 +2980,10 @@
         <v>手机</v>
       </c>
       <c r="K68" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L68" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="69">
@@ -3018,7 +3018,7 @@
         <v>手机</v>
       </c>
       <c r="K69" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L69" t="str">
         <v>济南中心仓</v>
@@ -3056,10 +3056,10 @@
         <v>手机</v>
       </c>
       <c r="K70" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L70" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="71">
@@ -3094,10 +3094,10 @@
         <v>手机</v>
       </c>
       <c r="K71" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L71" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="72">
@@ -3132,10 +3132,10 @@
         <v>手机</v>
       </c>
       <c r="K72" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L72" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="73">
@@ -3170,10 +3170,10 @@
         <v>手机</v>
       </c>
       <c r="K73" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L73" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="74">
@@ -3208,10 +3208,10 @@
         <v>手机</v>
       </c>
       <c r="K74" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L74" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="75">
@@ -3246,7 +3246,7 @@
         <v>手机</v>
       </c>
       <c r="K75" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L75" t="str">
         <v>昆明中心仓</v>
@@ -3284,7 +3284,7 @@
         <v>手机</v>
       </c>
       <c r="K76" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -3322,7 +3322,7 @@
         <v>手机</v>
       </c>
       <c r="K77" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L77" t="str">
         <v>昆明中心仓</v>
@@ -3360,7 +3360,7 @@
         <v>手机</v>
       </c>
       <c r="K78" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L78" t="str">
         <v>郑州中心仓</v>
@@ -3398,7 +3398,7 @@
         <v>手机</v>
       </c>
       <c r="K79" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L79" t="str">
         <v>昆明中心仓</v>
@@ -3436,10 +3436,10 @@
         <v>手机</v>
       </c>
       <c r="K80" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L80" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="81">
@@ -3474,10 +3474,10 @@
         <v>笔记本</v>
       </c>
       <c r="K81" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L81" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="82">
@@ -3512,7 +3512,7 @@
         <v>手机</v>
       </c>
       <c r="K82" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L82" t="str">
         <v>深圳中心仓</v>
@@ -3550,7 +3550,7 @@
         <v>手机</v>
       </c>
       <c r="K83" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L83" t="str">
         <v>郑州中心仓</v>
@@ -3588,7 +3588,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K84" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L84" t="str">
         <v>济南中心仓</v>
@@ -3626,7 +3626,7 @@
         <v>手机</v>
       </c>
       <c r="K85" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L85" t="str">
         <v>昆明中心仓</v>
@@ -3664,10 +3664,10 @@
         <v>手机</v>
       </c>
       <c r="K86" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L86" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="87">
@@ -3702,7 +3702,7 @@
         <v>手机</v>
       </c>
       <c r="K87" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L87" t="str">
         <v>昆明中心仓</v>
@@ -3740,7 +3740,7 @@
         <v>手机</v>
       </c>
       <c r="K88" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L88" t="str">
         <v>南京中心仓</v>
@@ -3778,7 +3778,7 @@
         <v>手机</v>
       </c>
       <c r="K89" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -3817,7 +3817,7 @@
         <v>手机</v>
       </c>
       <c r="K90" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L90" t="str">
         <v>合肥中心仓</v>
@@ -3856,7 +3856,7 @@
         <v>手机</v>
       </c>
       <c r="K91" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L91" t="str">
         <v>合肥中心仓</v>
@@ -3894,7 +3894,7 @@
         <v>手机</v>
       </c>
       <c r="K92" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L92" t="str">
         <v>南京中心仓</v>
@@ -3932,7 +3932,7 @@
         <v>手机</v>
       </c>
       <c r="K93" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L93" t="str">
         <v>昆明中心仓</v>
@@ -3970,10 +3970,10 @@
         <v>手机</v>
       </c>
       <c r="K94" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L94" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="95">
@@ -4008,10 +4008,10 @@
         <v>手机</v>
       </c>
       <c r="K95" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L95" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="96">
@@ -4046,10 +4046,10 @@
         <v>手机</v>
       </c>
       <c r="K96" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L96" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="97" xml:space="preserve">
@@ -4085,7 +4085,7 @@
         <v>手机</v>
       </c>
       <c r="K97" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L97" t="str">
         <v>南京中心仓</v>
@@ -4123,10 +4123,10 @@
         <v>手机</v>
       </c>
       <c r="K98" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L98" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="99">
@@ -4161,10 +4161,10 @@
         <v>手机</v>
       </c>
       <c r="K99" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L99" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="100">
@@ -4199,10 +4199,10 @@
         <v>手机</v>
       </c>
       <c r="K100" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L100" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="101">
@@ -4237,7 +4237,7 @@
         <v>笔记本</v>
       </c>
       <c r="K101" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L101" t="str">
         <v>郑州中心仓</v>
@@ -4275,7 +4275,7 @@
         <v>笔记本</v>
       </c>
       <c r="K102" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L102" t="str">
         <v>郑州中心仓</v>
@@ -4313,7 +4313,7 @@
         <v>笔记本</v>
       </c>
       <c r="K103" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L103" t="str">
         <v>郑州中心仓</v>
@@ -4351,7 +4351,7 @@
         <v>手机</v>
       </c>
       <c r="K104" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L104" t="str">
         <v>广州中心仓</v>
@@ -4389,10 +4389,10 @@
         <v>手机</v>
       </c>
       <c r="K105" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L105" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="106">
@@ -4427,10 +4427,10 @@
         <v>手机</v>
       </c>
       <c r="K106" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L106" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="107">
@@ -4465,10 +4465,10 @@
         <v>手机</v>
       </c>
       <c r="K107" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L107" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="108" xml:space="preserve">
@@ -4504,10 +4504,10 @@
         <v>笔记本</v>
       </c>
       <c r="K108" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L108" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="109">
@@ -4542,10 +4542,10 @@
         <v>手机</v>
       </c>
       <c r="K109" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L109" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="110">
@@ -4580,10 +4580,10 @@
         <v>手机</v>
       </c>
       <c r="K110" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L110" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="111">
@@ -4618,10 +4618,10 @@
         <v>手机</v>
       </c>
       <c r="K111" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L111" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="112" xml:space="preserve">
@@ -4657,10 +4657,10 @@
         <v>手机</v>
       </c>
       <c r="K112" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L112" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="113">
@@ -4695,7 +4695,7 @@
         <v>手机</v>
       </c>
       <c r="K113" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L113" t="str">
         <v>合肥中心仓</v>
@@ -4733,7 +4733,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K114" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L114" t="str">
         <v/>
@@ -4771,7 +4771,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K115" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L115" t="str">
         <v/>
@@ -4809,7 +4809,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K116" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L116" t="str">
         <v/>
@@ -4847,7 +4847,7 @@
         <v>手机</v>
       </c>
       <c r="K117" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L117" t="str">
         <v>昆明中心仓</v>
@@ -4885,7 +4885,7 @@
         <v>手机</v>
       </c>
       <c r="K118" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L118" t="str">
         <v>昆明中心仓</v>
@@ -4923,10 +4923,10 @@
         <v>手机</v>
       </c>
       <c r="K119" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L119" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="120">
@@ -4961,10 +4961,10 @@
         <v>手机</v>
       </c>
       <c r="K120" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L120" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="121">
@@ -4999,10 +4999,10 @@
         <v>手机</v>
       </c>
       <c r="K121" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L121" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="122">
@@ -5037,7 +5037,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K122" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L122" t="str">
         <v>南昌中心仓</v>
@@ -5075,7 +5075,7 @@
         <v>手机</v>
       </c>
       <c r="K123" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L123" t="str">
         <v>昆明中心仓</v>
@@ -5113,10 +5113,10 @@
         <v>笔记本</v>
       </c>
       <c r="K124" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L124" t="str">
-        <v/>
+        <v>长沙中心仓</v>
       </c>
     </row>
     <row r="125">
@@ -5151,10 +5151,10 @@
         <v>手机</v>
       </c>
       <c r="K125" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L125" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="126" xml:space="preserve">
@@ -5190,7 +5190,7 @@
         <v>手机</v>
       </c>
       <c r="K126" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L126" t="str">
         <v>南京中心仓</v>
@@ -5228,10 +5228,10 @@
         <v>手机</v>
       </c>
       <c r="K127" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L127" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="128">
@@ -5266,10 +5266,10 @@
         <v>手机</v>
       </c>
       <c r="K128" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L128" t="str">
-        <v/>
+        <v>武汉中心仓</v>
       </c>
     </row>
     <row r="129">
@@ -5304,7 +5304,7 @@
         <v>手机</v>
       </c>
       <c r="K129" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L129" t="str">
         <v>合肥中心仓</v>
@@ -5342,10 +5342,10 @@
         <v>笔记本</v>
       </c>
       <c r="K130" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L130" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="131">
@@ -5380,7 +5380,7 @@
         <v>手机</v>
       </c>
       <c r="K131" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L131" t="str">
         <v>成都中心仓</v>
@@ -5418,10 +5418,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K132" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L132" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="133">
@@ -5456,7 +5456,7 @@
         <v>手机</v>
       </c>
       <c r="K133" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L133" t="str">
         <v>郑州中心仓</v>
@@ -5494,7 +5494,7 @@
         <v>手机</v>
       </c>
       <c r="K134" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L134" t="str">
         <v>郑州中心仓</v>
@@ -5532,7 +5532,7 @@
         <v>手机</v>
       </c>
       <c r="K135" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L135" t="str">
         <v>郑州中心仓</v>
@@ -5570,7 +5570,7 @@
         <v>手机</v>
       </c>
       <c r="K136" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L136" t="str">
         <v>济南中心仓</v>
@@ -5608,10 +5608,10 @@
         <v>手机</v>
       </c>
       <c r="K137" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L137" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="138">
@@ -5646,7 +5646,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K138" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L138" t="str">
         <v/>
@@ -5684,7 +5684,7 @@
         <v>手机</v>
       </c>
       <c r="K139" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L139" t="str">
         <v>南京中心仓</v>
@@ -5722,10 +5722,10 @@
         <v>手机</v>
       </c>
       <c r="K140" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L140" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="141">
@@ -5760,10 +5760,10 @@
         <v>手机</v>
       </c>
       <c r="K141" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L141" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="142">
@@ -5798,10 +5798,10 @@
         <v>手机</v>
       </c>
       <c r="K142" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L142" t="str">
-        <v/>
+        <v>武汉中心仓</v>
       </c>
     </row>
     <row r="143">
@@ -5836,7 +5836,7 @@
         <v>手机</v>
       </c>
       <c r="K143" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L143" t="str">
         <v>济南中心仓</v>
@@ -5874,10 +5874,10 @@
         <v>手机</v>
       </c>
       <c r="K144" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L144" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="145">
@@ -5912,7 +5912,7 @@
         <v>手机</v>
       </c>
       <c r="K145" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L145" t="str">
         <v>济南中心仓</v>
@@ -5950,10 +5950,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K146" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L146" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="147">
@@ -5988,10 +5988,10 @@
         <v>手机</v>
       </c>
       <c r="K147" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L147" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="148">
@@ -6026,10 +6026,10 @@
         <v>手机</v>
       </c>
       <c r="K148" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L148" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="149">
@@ -6064,7 +6064,7 @@
         <v>手机</v>
       </c>
       <c r="K149" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L149" t="str">
         <v/>
@@ -6102,7 +6102,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K150" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L150" t="str">
         <v>深圳中心仓</v>
@@ -6140,10 +6140,10 @@
         <v>手机</v>
       </c>
       <c r="K151" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L151" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="152">
@@ -6178,7 +6178,7 @@
         <v>手机</v>
       </c>
       <c r="K152" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L152" t="str">
         <v>北京中心仓</v>
@@ -6216,7 +6216,7 @@
         <v>手机</v>
       </c>
       <c r="K153" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L153" t="str">
         <v>合肥中心仓</v>
@@ -6254,10 +6254,10 @@
         <v>手机</v>
       </c>
       <c r="K154" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L154" t="str">
-        <v/>
+        <v>济南中心仓</v>
       </c>
     </row>
     <row r="155">
@@ -6292,7 +6292,7 @@
         <v>手机</v>
       </c>
       <c r="K155" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L155" t="str">
         <v>昆明中心仓</v>
@@ -6330,7 +6330,7 @@
         <v>手机</v>
       </c>
       <c r="K156" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L156" t="str">
         <v>济南中心仓</v>
@@ -6368,7 +6368,7 @@
         <v>手机</v>
       </c>
       <c r="K157" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L157" t="str">
         <v>合肥中心仓</v>
@@ -6406,7 +6406,7 @@
         <v>手机</v>
       </c>
       <c r="K158" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L158" t="str">
         <v>济南中心仓</v>
@@ -6444,7 +6444,7 @@
         <v>手机</v>
       </c>
       <c r="K159" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L159" t="str">
         <v>南昌中心仓</v>
@@ -6482,10 +6482,10 @@
         <v>手机</v>
       </c>
       <c r="K160" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L160" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="161">
@@ -6520,7 +6520,7 @@
         <v>手机</v>
       </c>
       <c r="K161" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L161" t="str">
         <v>南京中心仓</v>
@@ -6558,7 +6558,7 @@
         <v>手机</v>
       </c>
       <c r="K162" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L162" t="str">
         <v>南京中心仓</v>
@@ -6596,7 +6596,7 @@
         <v>手机</v>
       </c>
       <c r="K163" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L163" t="str">
         <v>北京中心仓</v>
@@ -6634,7 +6634,7 @@
         <v>手机</v>
       </c>
       <c r="K164" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L164" t="str">
         <v/>
@@ -6672,10 +6672,10 @@
         <v>手机</v>
       </c>
       <c r="K165" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L165" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="166">
@@ -6710,10 +6710,10 @@
         <v>手机</v>
       </c>
       <c r="K166" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L166" t="str">
-        <v/>
+        <v>郑州中心仓</v>
       </c>
     </row>
     <row r="167">
@@ -6748,10 +6748,10 @@
         <v>手机</v>
       </c>
       <c r="K167" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L167" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="168">
@@ -6786,7 +6786,7 @@
         <v>手机</v>
       </c>
       <c r="K168" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L168" t="str">
         <v>成都中心仓</v>
@@ -6824,10 +6824,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K169" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L169" t="str">
-        <v/>
+        <v>郑州中心仓</v>
       </c>
     </row>
     <row r="170">
@@ -6862,10 +6862,10 @@
         <v>手机</v>
       </c>
       <c r="K170" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L170" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="171">
@@ -6900,10 +6900,10 @@
         <v>手机</v>
       </c>
       <c r="K171" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L171" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="172">
@@ -6938,10 +6938,10 @@
         <v>智能手表</v>
       </c>
       <c r="K172" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L172" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="173">
@@ -6976,7 +6976,7 @@
         <v>手机</v>
       </c>
       <c r="K173" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L173" t="str">
         <v>成都中心仓</v>
@@ -7014,10 +7014,10 @@
         <v>手机</v>
       </c>
       <c r="K174" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L174" t="str">
-        <v/>
+        <v>济南中心仓</v>
       </c>
     </row>
     <row r="175">
@@ -7052,7 +7052,7 @@
         <v>手机</v>
       </c>
       <c r="K175" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L175" t="str">
         <v>合肥中心仓</v>
@@ -7090,10 +7090,10 @@
         <v>手机</v>
       </c>
       <c r="K176" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L176" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="177">
@@ -7128,7 +7128,7 @@
         <v>手机</v>
       </c>
       <c r="K177" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L177" t="str">
         <v>南京中心仓</v>
@@ -7166,7 +7166,7 @@
         <v>笔记本</v>
       </c>
       <c r="K178" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L178" t="str">
         <v>长沙中心仓</v>
@@ -7204,7 +7204,7 @@
         <v>手机</v>
       </c>
       <c r="K179" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L179" t="str">
         <v>深圳中心仓</v>
@@ -7242,7 +7242,7 @@
         <v>手机</v>
       </c>
       <c r="K180" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L180" t="str">
         <v>深圳中心仓</v>
@@ -7280,7 +7280,7 @@
         <v>手机</v>
       </c>
       <c r="K181" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L181" t="str">
         <v>深圳中心仓</v>
@@ -7318,7 +7318,7 @@
         <v>手机</v>
       </c>
       <c r="K182" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L182" t="str">
         <v>深圳中心仓</v>
@@ -7356,7 +7356,7 @@
         <v>手机</v>
       </c>
       <c r="K183" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L183" t="str">
         <v>合肥中心仓</v>
@@ -7394,7 +7394,7 @@
         <v>手机</v>
       </c>
       <c r="K184" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L184" t="str">
         <v>南京中心仓</v>
@@ -7432,7 +7432,7 @@
         <v>手机</v>
       </c>
       <c r="K185" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L185" t="str">
         <v>济南中心仓</v>
@@ -7470,10 +7470,10 @@
         <v>手机</v>
       </c>
       <c r="K186" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L186" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="187">
@@ -7508,7 +7508,7 @@
         <v>智能手表</v>
       </c>
       <c r="K187" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L187" t="str">
         <v>深圳中心仓</v>
@@ -7546,7 +7546,7 @@
         <v>手机</v>
       </c>
       <c r="K188" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L188" t="str">
         <v>成都中心仓</v>
@@ -7584,7 +7584,7 @@
         <v>手机</v>
       </c>
       <c r="K189" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L189" t="str">
         <v>重庆中心仓</v>
@@ -7622,7 +7622,7 @@
         <v>手机</v>
       </c>
       <c r="K190" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L190" t="str">
         <v/>
@@ -7660,7 +7660,7 @@
         <v>手机</v>
       </c>
       <c r="K191" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L191" t="str">
         <v>南京中心仓</v>
@@ -7698,7 +7698,7 @@
         <v>手机</v>
       </c>
       <c r="K192" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L192" t="str">
         <v>天津中心仓</v>
@@ -7736,7 +7736,7 @@
         <v>手机</v>
       </c>
       <c r="K193" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L193" t="str">
         <v>杭州中心仓</v>
@@ -7774,7 +7774,7 @@
         <v>手机</v>
       </c>
       <c r="K194" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L194" t="str">
         <v>南京中心仓</v>
@@ -7812,10 +7812,10 @@
         <v>手机</v>
       </c>
       <c r="K195" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L195" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="196">
@@ -7850,7 +7850,7 @@
         <v>手机</v>
       </c>
       <c r="K196" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L196" t="str">
         <v>南昌中心仓</v>
@@ -7888,7 +7888,7 @@
         <v>手机</v>
       </c>
       <c r="K197" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L197" t="str">
         <v>杭州中心仓</v>
@@ -7926,7 +7926,7 @@
         <v>手机</v>
       </c>
       <c r="K198" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L198" t="str">
         <v>合肥中心仓</v>
@@ -7964,7 +7964,7 @@
         <v>手机</v>
       </c>
       <c r="K199" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L199" t="str">
         <v>郑州中心仓</v>
@@ -8002,7 +8002,7 @@
         <v>手机</v>
       </c>
       <c r="K200" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L200" t="str">
         <v>济南中心仓</v>
@@ -8040,7 +8040,7 @@
         <v>手机</v>
       </c>
       <c r="K201" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L201" t="str">
         <v>昆明中心仓</v>
@@ -8078,7 +8078,7 @@
         <v>手机</v>
       </c>
       <c r="K202" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L202" t="str">
         <v>昆明中心仓</v>
@@ -8116,7 +8116,7 @@
         <v>手机</v>
       </c>
       <c r="K203" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L203" t="str">
         <v/>
@@ -8154,10 +8154,10 @@
         <v>手机</v>
       </c>
       <c r="K204" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L204" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="205">
@@ -8192,7 +8192,7 @@
         <v>耳机/耳麦</v>
       </c>
       <c r="K205" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L205" t="str">
         <v>杭州中心仓</v>
@@ -8230,7 +8230,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K206" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L206" t="str">
         <v>深圳中心仓</v>
@@ -8268,7 +8268,7 @@
         <v>手机</v>
       </c>
       <c r="K207" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L207" t="str">
         <v>南昌中心仓</v>
@@ -8306,7 +8306,7 @@
         <v>手机</v>
       </c>
       <c r="K208" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L208" t="str">
         <v>合肥中心仓</v>
@@ -8344,7 +8344,7 @@
         <v>手机</v>
       </c>
       <c r="K209" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L209" t="str">
         <v/>
@@ -8382,7 +8382,7 @@
         <v>手机</v>
       </c>
       <c r="K210" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L210" t="str">
         <v>济南中心仓</v>
@@ -8420,7 +8420,7 @@
         <v>手机</v>
       </c>
       <c r="K211" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L211" t="str">
         <v>深圳中心仓</v>
@@ -8458,7 +8458,7 @@
         <v>手机</v>
       </c>
       <c r="K212" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L212" t="str">
         <v>深圳中心仓</v>
@@ -8496,7 +8496,7 @@
         <v>手机</v>
       </c>
       <c r="K213" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L213" t="str">
         <v>深圳中心仓</v>
@@ -8534,7 +8534,7 @@
         <v>手机</v>
       </c>
       <c r="K214" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L214" t="str">
         <v>深圳中心仓</v>
@@ -8572,7 +8572,7 @@
         <v>手机</v>
       </c>
       <c r="K215" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L215" t="str">
         <v>深圳中心仓</v>
@@ -8610,7 +8610,7 @@
         <v>手机</v>
       </c>
       <c r="K216" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L216" t="str">
         <v>深圳中心仓</v>
@@ -8648,7 +8648,7 @@
         <v>手机</v>
       </c>
       <c r="K217" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L217" t="str">
         <v>深圳中心仓</v>
@@ -8686,7 +8686,7 @@
         <v>手机</v>
       </c>
       <c r="K218" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L218" t="str">
         <v>济南中心仓</v>
@@ -8724,7 +8724,7 @@
         <v>手机</v>
       </c>
       <c r="K219" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L219" t="str">
         <v>济南中心仓</v>
@@ -8762,7 +8762,7 @@
         <v>手机</v>
       </c>
       <c r="K220" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L220" t="str">
         <v>武汉中心仓</v>
@@ -8800,7 +8800,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K221" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L221" t="str">
         <v>深圳中心仓</v>
@@ -8838,10 +8838,10 @@
         <v>手机</v>
       </c>
       <c r="K222" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L222" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="223">
@@ -8876,7 +8876,7 @@
         <v>笔记本</v>
       </c>
       <c r="K223" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L223" t="str">
         <v>南京中心仓</v>
@@ -8914,7 +8914,7 @@
         <v>手机</v>
       </c>
       <c r="K224" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L224" t="str">
         <v>合肥中心仓</v>
@@ -8952,10 +8952,10 @@
         <v>手机</v>
       </c>
       <c r="K225" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L225" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="226">
@@ -8990,7 +8990,7 @@
         <v>笔记本</v>
       </c>
       <c r="K226" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L226" t="str">
         <v>南京中心仓</v>
@@ -9028,10 +9028,10 @@
         <v>手机</v>
       </c>
       <c r="K227" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L227" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="228">
@@ -9066,7 +9066,7 @@
         <v>手机</v>
       </c>
       <c r="K228" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L228" t="str">
         <v>沈阳中心仓</v>
@@ -9104,10 +9104,10 @@
         <v>手机</v>
       </c>
       <c r="K229" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L229" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="230">
@@ -9142,7 +9142,7 @@
         <v>手机</v>
       </c>
       <c r="K230" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L230" t="str">
         <v>南昌中心仓</v>
@@ -9180,7 +9180,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K231" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L231" t="str">
         <v>深圳中心仓</v>
@@ -9218,7 +9218,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K232" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L232" t="str">
         <v>深圳中心仓</v>
@@ -9256,7 +9256,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K233" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L233" t="str">
         <v>深圳中心仓</v>
@@ -9294,7 +9294,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K234" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L234" t="str">
         <v>深圳中心仓</v>
@@ -9332,7 +9332,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K235" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L235" t="str">
         <v>深圳中心仓</v>
@@ -9370,10 +9370,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K236" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L236" t="str">
-        <v/>
+        <v>昆明中心仓</v>
       </c>
     </row>
     <row r="237">
@@ -9408,7 +9408,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K237" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L237" t="str">
         <v>深圳中心仓</v>
@@ -9446,7 +9446,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K238" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L238" t="str">
         <v>深圳中心仓</v>
@@ -9484,7 +9484,7 @@
         <v>手机</v>
       </c>
       <c r="K239" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L239" t="str">
         <v>深圳中心仓</v>
@@ -9522,7 +9522,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K240" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L240" t="str">
         <v>深圳中心仓</v>
@@ -9560,7 +9560,7 @@
         <v>手机</v>
       </c>
       <c r="K241" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L241" t="str">
         <v/>
@@ -9598,7 +9598,7 @@
         <v>手机</v>
       </c>
       <c r="K242" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L242" t="str">
         <v>南昌中心仓</v>
@@ -9636,7 +9636,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K243" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L243" t="str">
         <v>深圳中心仓</v>
@@ -9674,10 +9674,10 @@
         <v>手机</v>
       </c>
       <c r="K244" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L244" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="245">
@@ -9712,7 +9712,7 @@
         <v>笔记本</v>
       </c>
       <c r="K245" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L245" t="str">
         <v>南京中心仓</v>
@@ -9750,7 +9750,7 @@
         <v>手机</v>
       </c>
       <c r="K246" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L246" t="str">
         <v>南京中心仓</v>
@@ -9788,7 +9788,7 @@
         <v>手机</v>
       </c>
       <c r="K247" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L247" t="str">
         <v>南京中心仓</v>
@@ -9826,10 +9826,10 @@
         <v>手机</v>
       </c>
       <c r="K248" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L248" t="str">
-        <v/>
+        <v>郑州中心仓</v>
       </c>
     </row>
     <row r="249">
@@ -9864,7 +9864,7 @@
         <v>手机</v>
       </c>
       <c r="K249" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L249" t="str">
         <v>深圳中心仓</v>
@@ -9902,7 +9902,7 @@
         <v>手机</v>
       </c>
       <c r="K250" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L250" t="str">
         <v>福州中心仓</v>
@@ -9940,7 +9940,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K251" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L251" t="str">
         <v/>
@@ -9978,7 +9978,7 @@
         <v>手机</v>
       </c>
       <c r="K252" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L252" t="str">
         <v>济南中心仓</v>
@@ -10010,16 +10010,16 @@
         <v>复测拦截内存更换，爬虫，客服和网上查询均没有刚换，机器有两个版本；16G版本是板载16，32G版本是板载16+插槽16      麻烦让QA教一下板载内存怎么更换</v>
       </c>
       <c r="I253" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
       <c r="J253" t="str">
         <v>笔记本</v>
       </c>
       <c r="K253" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L253" t="str">
-        <v/>
+        <v>济南中心仓</v>
       </c>
     </row>
     <row r="254">
@@ -10054,7 +10054,7 @@
         <v>手机</v>
       </c>
       <c r="K254" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L254" t="str">
         <v>杭州中心仓</v>
@@ -10092,7 +10092,7 @@
         <v>手机</v>
       </c>
       <c r="K255" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L255" t="str">
         <v>重庆中心仓</v>
@@ -10130,7 +10130,7 @@
         <v>手机</v>
       </c>
       <c r="K256" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L256" t="str">
         <v>济南中心仓</v>
@@ -10168,10 +10168,10 @@
         <v>手机</v>
       </c>
       <c r="K257" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L257" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="258">
@@ -10206,10 +10206,10 @@
         <v>智能手表</v>
       </c>
       <c r="K258" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L258" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="259">
@@ -10244,10 +10244,10 @@
         <v>手机</v>
       </c>
       <c r="K259" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L259" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="260">
@@ -10282,7 +10282,7 @@
         <v>手机</v>
       </c>
       <c r="K260" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L260" t="str">
         <v>南昌中心仓</v>
@@ -10320,7 +10320,7 @@
         <v>手机</v>
       </c>
       <c r="K261" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L261" t="str">
         <v>广州中心仓</v>
@@ -10358,7 +10358,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K262" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L262" t="str">
         <v>沈阳中心仓</v>
@@ -10396,7 +10396,7 @@
         <v>手机</v>
       </c>
       <c r="K263" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L263" t="str">
         <v>南昌中心仓</v>
@@ -10434,7 +10434,7 @@
         <v>手机</v>
       </c>
       <c r="K264" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L264" t="str">
         <v/>
@@ -10472,7 +10472,7 @@
         <v>手机</v>
       </c>
       <c r="K265" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L265" t="str">
         <v>深圳中心仓</v>
@@ -10511,7 +10511,7 @@
         <v>手机</v>
       </c>
       <c r="K266" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L266" t="str">
         <v>深圳中心仓</v>
@@ -10549,7 +10549,7 @@
         <v>手机</v>
       </c>
       <c r="K267" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L267" t="str">
         <v>杭州中心仓</v>
@@ -10588,7 +10588,7 @@
         <v>手机</v>
       </c>
       <c r="K268" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L268" t="str">
         <v>南昌中心仓</v>
@@ -10626,10 +10626,10 @@
         <v>手机</v>
       </c>
       <c r="K269" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L269" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="270">
@@ -10664,7 +10664,7 @@
         <v>手机</v>
       </c>
       <c r="K270" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L270" t="str">
         <v/>
@@ -10702,10 +10702,10 @@
         <v>手机</v>
       </c>
       <c r="K271" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L271" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="272">
@@ -10740,10 +10740,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K272" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L272" t="str">
-        <v/>
+        <v>济南中心仓</v>
       </c>
     </row>
     <row r="273">
@@ -10778,10 +10778,10 @@
         <v>手机</v>
       </c>
       <c r="K273" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L273" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="274">
@@ -10816,10 +10816,10 @@
         <v>手机</v>
       </c>
       <c r="K274" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L274" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="275">
@@ -10854,7 +10854,7 @@
         <v>手机</v>
       </c>
       <c r="K275" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L275" t="str">
         <v/>
@@ -10892,7 +10892,7 @@
         <v>手机</v>
       </c>
       <c r="K276" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L276" t="str">
         <v>杭州中心仓</v>
@@ -10930,7 +10930,7 @@
         <v>手机</v>
       </c>
       <c r="K277" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L277" t="str">
         <v>深圳中心仓</v>
@@ -10968,7 +10968,7 @@
         <v>手机</v>
       </c>
       <c r="K278" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L278" t="str">
         <v>深圳中心仓</v>
@@ -11006,10 +11006,10 @@
         <v>手机</v>
       </c>
       <c r="K279" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L279" t="str">
-        <v/>
+        <v>西安中心仓</v>
       </c>
     </row>
     <row r="280">
@@ -11044,7 +11044,7 @@
         <v>手机</v>
       </c>
       <c r="K280" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L280" t="str">
         <v>济南中心仓</v>
@@ -11082,7 +11082,7 @@
         <v>手机</v>
       </c>
       <c r="K281" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L281" t="str">
         <v>济南中心仓</v>
@@ -11121,10 +11121,10 @@
         <v>手机</v>
       </c>
       <c r="K282" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L282" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="283">
@@ -11159,7 +11159,7 @@
         <v>手机</v>
       </c>
       <c r="K283" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L283" t="str">
         <v>杭州中心仓</v>
@@ -11197,7 +11197,7 @@
         <v>手机</v>
       </c>
       <c r="K284" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L284" t="str">
         <v/>
@@ -11235,7 +11235,7 @@
         <v>笔记本</v>
       </c>
       <c r="K285" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L285" t="str">
         <v>南京中心仓</v>
@@ -11273,7 +11273,7 @@
         <v>手机</v>
       </c>
       <c r="K286" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L286" t="str">
         <v>深圳中心仓</v>
@@ -11311,7 +11311,7 @@
         <v>手机</v>
       </c>
       <c r="K287" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L287" t="str">
         <v>深圳中心仓</v>
@@ -11349,7 +11349,7 @@
         <v>手机</v>
       </c>
       <c r="K288" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L288" t="str">
         <v>深圳中心仓</v>
@@ -11387,7 +11387,7 @@
         <v>手机</v>
       </c>
       <c r="K289" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L289" t="str">
         <v>深圳中心仓</v>
@@ -11425,7 +11425,7 @@
         <v>手机</v>
       </c>
       <c r="K290" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L290" t="str">
         <v>深圳中心仓</v>
@@ -11463,7 +11463,7 @@
         <v>手机</v>
       </c>
       <c r="K291" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L291" t="str">
         <v>深圳中心仓</v>
@@ -11501,7 +11501,7 @@
         <v>手机</v>
       </c>
       <c r="K292" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L292" t="str">
         <v>深圳中心仓</v>
@@ -11539,7 +11539,7 @@
         <v>手机</v>
       </c>
       <c r="K293" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L293" t="str">
         <v>深圳中心仓</v>
@@ -11577,7 +11577,7 @@
         <v>手机</v>
       </c>
       <c r="K294" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L294" t="str">
         <v>郑州中心仓</v>
@@ -11615,7 +11615,7 @@
         <v>手机</v>
       </c>
       <c r="K295" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L295" t="str">
         <v>昆明中心仓</v>
@@ -11653,7 +11653,7 @@
         <v>手机</v>
       </c>
       <c r="K296" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L296" t="str">
         <v>合肥中心仓</v>
@@ -11691,7 +11691,7 @@
         <v>手机</v>
       </c>
       <c r="K297" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L297" t="str">
         <v>合肥中心仓</v>
@@ -11729,7 +11729,7 @@
         <v>手机</v>
       </c>
       <c r="K298" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L298" t="str">
         <v/>
@@ -11767,7 +11767,7 @@
         <v>智能手表</v>
       </c>
       <c r="K299" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L299" t="str">
         <v>深圳中心仓</v>
@@ -11805,10 +11805,10 @@
         <v>手机</v>
       </c>
       <c r="K300" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L300" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="301">
@@ -11843,10 +11843,10 @@
         <v>手机</v>
       </c>
       <c r="K301" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L301" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="302">
@@ -11881,10 +11881,10 @@
         <v>手机</v>
       </c>
       <c r="K302" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L302" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="303">
@@ -11919,10 +11919,10 @@
         <v>手机</v>
       </c>
       <c r="K303" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L303" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="304">
@@ -11957,10 +11957,10 @@
         <v>手机</v>
       </c>
       <c r="K304" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L304" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="305">
@@ -11995,10 +11995,10 @@
         <v>手机</v>
       </c>
       <c r="K305" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L305" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="306">
@@ -12033,10 +12033,10 @@
         <v>手机</v>
       </c>
       <c r="K306" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L306" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="307">
@@ -12071,7 +12071,7 @@
         <v>手机</v>
       </c>
       <c r="K307" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L307" t="str">
         <v>郑州中心仓</v>
@@ -12109,7 +12109,7 @@
         <v>手机</v>
       </c>
       <c r="K308" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L308" t="str">
         <v>深圳中心仓</v>
@@ -12147,7 +12147,7 @@
         <v>手机</v>
       </c>
       <c r="K309" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L309" t="str">
         <v/>
@@ -12185,7 +12185,7 @@
         <v>手机</v>
       </c>
       <c r="K310" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L310" t="str">
         <v>南京中心仓</v>
@@ -12223,7 +12223,7 @@
         <v>手机</v>
       </c>
       <c r="K311" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L311" t="str">
         <v>昆明中心仓</v>
@@ -12261,7 +12261,7 @@
         <v>手机</v>
       </c>
       <c r="K312" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L312" t="str">
         <v>南京中心仓</v>
@@ -12299,10 +12299,10 @@
         <v>手机</v>
       </c>
       <c r="K313" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L313" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="314">
@@ -12337,7 +12337,7 @@
         <v>笔记本</v>
       </c>
       <c r="K314" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L314" t="str">
         <v>南京中心仓</v>
@@ -12375,10 +12375,10 @@
         <v>手机</v>
       </c>
       <c r="K315" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L315" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="316">
@@ -12413,7 +12413,7 @@
         <v>手机</v>
       </c>
       <c r="K316" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L316" t="str">
         <v>长沙中心仓</v>
@@ -12451,7 +12451,7 @@
         <v>手机</v>
       </c>
       <c r="K317" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L317" t="str">
         <v>深圳中心仓</v>
@@ -12489,7 +12489,7 @@
         <v>手机</v>
       </c>
       <c r="K318" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L318" t="str">
         <v>南京中心仓</v>
@@ -12527,7 +12527,7 @@
         <v>手机</v>
       </c>
       <c r="K319" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L319" t="str">
         <v>南京中心仓</v>
@@ -12565,7 +12565,7 @@
         <v>手机</v>
       </c>
       <c r="K320" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L320" t="str">
         <v>南京中心仓</v>
@@ -12603,10 +12603,10 @@
         <v>手机</v>
       </c>
       <c r="K321" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L321" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="322">
@@ -12641,7 +12641,7 @@
         <v>手机</v>
       </c>
       <c r="K322" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L322" t="str">
         <v>武汉中心仓</v>
@@ -12679,7 +12679,7 @@
         <v>手机</v>
       </c>
       <c r="K323" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L323" t="str">
         <v>杭州中心仓</v>
@@ -12717,10 +12717,10 @@
         <v>智能手表</v>
       </c>
       <c r="K324" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L324" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="325">
@@ -12755,7 +12755,7 @@
         <v>手机</v>
       </c>
       <c r="K325" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L325" t="str">
         <v>深圳中心仓</v>
@@ -12793,7 +12793,7 @@
         <v>手机</v>
       </c>
       <c r="K326" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L326" t="str">
         <v>深圳中心仓</v>
@@ -12832,7 +12832,7 @@
         <v>手机</v>
       </c>
       <c r="K327" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L327" t="str">
         <v>深圳中心仓</v>
@@ -12870,7 +12870,7 @@
         <v>手机</v>
       </c>
       <c r="K328" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L328" t="str">
         <v>深圳中心仓</v>
@@ -12908,7 +12908,7 @@
         <v>手机</v>
       </c>
       <c r="K329" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L329" t="str">
         <v>深圳中心仓</v>
@@ -12946,7 +12946,7 @@
         <v>手机</v>
       </c>
       <c r="K330" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L330" t="str">
         <v>合肥中心仓</v>
@@ -12984,7 +12984,7 @@
         <v>手机</v>
       </c>
       <c r="K331" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L331" t="str">
         <v>深圳中心仓</v>
@@ -13022,7 +13022,7 @@
         <v>手机</v>
       </c>
       <c r="K332" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L332" t="str">
         <v>深圳中心仓</v>
@@ -13060,7 +13060,7 @@
         <v>手机</v>
       </c>
       <c r="K333" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L333" t="str">
         <v>深圳中心仓</v>
@@ -13098,7 +13098,7 @@
         <v>手机</v>
       </c>
       <c r="K334" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L334" t="str">
         <v>深圳中心仓</v>
@@ -13136,7 +13136,7 @@
         <v>手机</v>
       </c>
       <c r="K335" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L335" t="str">
         <v>深圳中心仓</v>
@@ -13174,7 +13174,7 @@
         <v>手机</v>
       </c>
       <c r="K336" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L336" t="str">
         <v>深圳中心仓</v>
@@ -13212,7 +13212,7 @@
         <v>笔记本</v>
       </c>
       <c r="K337" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L337" t="str">
         <v>南京中心仓</v>
@@ -13250,7 +13250,7 @@
         <v>手机</v>
       </c>
       <c r="K338" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L338" t="str">
         <v>南京中心仓</v>
@@ -13288,7 +13288,7 @@
         <v>手机</v>
       </c>
       <c r="K339" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L339" t="str">
         <v>沈阳中心仓</v>
@@ -13326,7 +13326,7 @@
         <v>智能手表</v>
       </c>
       <c r="K340" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L340" t="str">
         <v>南京中心仓</v>
@@ -13364,7 +13364,7 @@
         <v>手机</v>
       </c>
       <c r="K341" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L341" t="str">
         <v>合肥中心仓</v>
@@ -13402,7 +13402,7 @@
         <v>手机</v>
       </c>
       <c r="K342" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L342" t="str">
         <v>重庆中心仓</v>
@@ -13440,10 +13440,10 @@
         <v>手机</v>
       </c>
       <c r="K343" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L343" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="344">
@@ -13478,7 +13478,7 @@
         <v>手机</v>
       </c>
       <c r="K344" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L344" t="str">
         <v>沈阳中心仓</v>
@@ -13516,7 +13516,7 @@
         <v>笔记本</v>
       </c>
       <c r="K345" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L345" t="str">
         <v>北京中心仓</v>
@@ -13554,10 +13554,10 @@
         <v>手机</v>
       </c>
       <c r="K346" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L346" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="347">
@@ -13592,10 +13592,10 @@
         <v>手机</v>
       </c>
       <c r="K347" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L347" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="348">
@@ -13630,10 +13630,10 @@
         <v>手机</v>
       </c>
       <c r="K348" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L348" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="349">
@@ -13668,10 +13668,10 @@
         <v>手机</v>
       </c>
       <c r="K349" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L349" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="350">
@@ -13706,10 +13706,10 @@
         <v>手机</v>
       </c>
       <c r="K350" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L350" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="351">
@@ -13744,10 +13744,10 @@
         <v>手机</v>
       </c>
       <c r="K351" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L351" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="352">
@@ -13782,7 +13782,7 @@
         <v>手机</v>
       </c>
       <c r="K352" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L352" t="str">
         <v>重庆中心仓</v>
@@ -13824,10 +13824,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K353" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L353" t="str">
-        <v/>
+        <v>西安中心仓</v>
       </c>
     </row>
     <row r="354">
@@ -13862,10 +13862,10 @@
         <v>手机</v>
       </c>
       <c r="K354" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L354" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="355">
@@ -13900,10 +13900,10 @@
         <v>手机</v>
       </c>
       <c r="K355" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L355" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="356">
@@ -13938,10 +13938,10 @@
         <v>手机</v>
       </c>
       <c r="K356" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L356" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="357">
@@ -13976,10 +13976,10 @@
         <v>手机</v>
       </c>
       <c r="K357" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L357" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="358">
@@ -14014,10 +14014,10 @@
         <v>手机</v>
       </c>
       <c r="K358" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L358" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="359">
@@ -14052,10 +14052,10 @@
         <v>手机</v>
       </c>
       <c r="K359" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L359" t="str">
-        <v/>
+        <v>福州中心仓</v>
       </c>
     </row>
     <row r="360">
@@ -14090,7 +14090,7 @@
         <v>手机</v>
       </c>
       <c r="K360" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L360" t="str">
         <v>深圳中心仓</v>
@@ -14128,7 +14128,7 @@
         <v>智能手表</v>
       </c>
       <c r="K361" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L361" t="str">
         <v>南京中心仓</v>
@@ -14166,7 +14166,7 @@
         <v>手机</v>
       </c>
       <c r="K362" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L362" t="str">
         <v>济南中心仓</v>
@@ -14204,7 +14204,7 @@
         <v>笔记本</v>
       </c>
       <c r="K363" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L363" t="str">
         <v>成都中心仓</v>
@@ -14242,7 +14242,7 @@
         <v>手机</v>
       </c>
       <c r="K364" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L364" t="str">
         <v>深圳中心仓</v>
@@ -14280,7 +14280,7 @@
         <v>手机</v>
       </c>
       <c r="K365" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L365" t="str">
         <v>深圳中心仓</v>
@@ -14318,7 +14318,7 @@
         <v>手机</v>
       </c>
       <c r="K366" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L366" t="str">
         <v>郑州中心仓</v>
@@ -14356,7 +14356,7 @@
         <v>手机</v>
       </c>
       <c r="K367" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L367" t="str">
         <v>杭州中心仓</v>
@@ -14394,7 +14394,7 @@
         <v>手机</v>
       </c>
       <c r="K368" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L368" t="str">
         <v>南京中心仓</v>
@@ -14432,10 +14432,10 @@
         <v>手机</v>
       </c>
       <c r="K369" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L369" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="370">
@@ -14470,7 +14470,7 @@
         <v/>
       </c>
       <c r="K370" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L370" t="str">
         <v>成都中心仓</v>
@@ -14508,7 +14508,7 @@
         <v>笔记本</v>
       </c>
       <c r="K371" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L371" t="str">
         <v>成都中心仓</v>
@@ -14547,10 +14547,10 @@
         <v>手机</v>
       </c>
       <c r="K372" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L372" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="373">
@@ -14585,10 +14585,10 @@
         <v>手机</v>
       </c>
       <c r="K373" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L373" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="374">
@@ -14623,7 +14623,7 @@
         <v>手机</v>
       </c>
       <c r="K374" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L374" t="str">
         <v>郑州中心仓</v>
@@ -14661,7 +14661,7 @@
         <v>手机</v>
       </c>
       <c r="K375" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L375" t="str">
         <v>郑州中心仓</v>
@@ -14699,7 +14699,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K376" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L376" t="str">
         <v>福州中心仓</v>
@@ -14737,7 +14737,7 @@
         <v>手机</v>
       </c>
       <c r="K377" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L377" t="str">
         <v>沈阳中心仓</v>
@@ -14775,10 +14775,10 @@
         <v>手机</v>
       </c>
       <c r="K378" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L378" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="379">
@@ -14813,7 +14813,7 @@
         <v>手机</v>
       </c>
       <c r="K379" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L379" t="str">
         <v>济南中心仓</v>
@@ -14854,7 +14854,7 @@
         <v>笔记本</v>
       </c>
       <c r="K380" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L380" t="str">
         <v>武汉中心仓</v>
@@ -14892,7 +14892,7 @@
         <v>笔记本</v>
       </c>
       <c r="K381" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L381" t="str">
         <v>南京中心仓</v>
@@ -14930,10 +14930,10 @@
         <v>手机</v>
       </c>
       <c r="K382" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L382" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="383">
@@ -14968,7 +14968,7 @@
         <v>手机</v>
       </c>
       <c r="K383" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L383" t="str">
         <v>深圳中心仓</v>
@@ -15006,7 +15006,7 @@
         <v>手机</v>
       </c>
       <c r="K384" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L384" t="str">
         <v>郑州中心仓</v>
@@ -15044,7 +15044,7 @@
         <v>手机</v>
       </c>
       <c r="K385" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L385" t="str">
         <v>深圳中心仓</v>
@@ -15082,10 +15082,10 @@
         <v>手机</v>
       </c>
       <c r="K386" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L386" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="387">
@@ -15120,7 +15120,7 @@
         <v>手机</v>
       </c>
       <c r="K387" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L387" t="str">
         <v>深圳中心仓</v>
@@ -15158,7 +15158,7 @@
         <v>手机</v>
       </c>
       <c r="K388" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L388" t="str">
         <v>石家庄中心仓</v>
@@ -15196,7 +15196,7 @@
         <v>手机</v>
       </c>
       <c r="K389" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L389" t="str">
         <v>杭州中心仓</v>
@@ -15234,7 +15234,7 @@
         <v>单电/微单套机</v>
       </c>
       <c r="K390" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L390" t="str">
         <v>成都中心仓</v>
@@ -15272,7 +15272,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K391" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L391" t="str">
         <v>南京中心仓</v>
@@ -15312,7 +15312,7 @@
         <v>手机</v>
       </c>
       <c r="K392" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L392" t="str">
         <v>南京中心仓</v>
@@ -15350,7 +15350,7 @@
         <v>手机</v>
       </c>
       <c r="K393" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L393" t="str">
         <v>深圳中心仓</v>
@@ -15388,7 +15388,7 @@
         <v>手机</v>
       </c>
       <c r="K394" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L394" t="str">
         <v>深圳中心仓</v>
@@ -15426,7 +15426,7 @@
         <v>手机</v>
       </c>
       <c r="K395" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L395" t="str">
         <v>深圳中心仓</v>
@@ -15464,7 +15464,7 @@
         <v>手机</v>
       </c>
       <c r="K396" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L396" t="str">
         <v>深圳中心仓</v>
@@ -15502,7 +15502,7 @@
         <v>手机</v>
       </c>
       <c r="K397" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L397" t="str">
         <v>深圳中心仓</v>
@@ -15540,7 +15540,7 @@
         <v>手机</v>
       </c>
       <c r="K398" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L398" t="str">
         <v>深圳中心仓</v>
@@ -15578,7 +15578,7 @@
         <v>手机</v>
       </c>
       <c r="K399" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L399" t="str">
         <v>武汉中心仓</v>
@@ -15616,7 +15616,7 @@
         <v>手机</v>
       </c>
       <c r="K400" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L400" t="str">
         <v/>
@@ -15654,7 +15654,7 @@
         <v>手机</v>
       </c>
       <c r="K401" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L401" t="str">
         <v>南京中心仓</v>
@@ -15692,7 +15692,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K402" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L402" t="str">
         <v/>
@@ -15730,7 +15730,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K403" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L403" t="str">
         <v/>
@@ -15768,7 +15768,7 @@
         <v>手机</v>
       </c>
       <c r="K404" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L404" t="str">
         <v>西安中心仓</v>
@@ -15806,7 +15806,7 @@
         <v>手机</v>
       </c>
       <c r="K405" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L405" t="str">
         <v>西安中心仓</v>
@@ -15844,7 +15844,7 @@
         <v>笔记本</v>
       </c>
       <c r="K406" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L406" t="str">
         <v>南京中心仓</v>
@@ -15882,7 +15882,7 @@
         <v>笔记本</v>
       </c>
       <c r="K407" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L407" t="str">
         <v>南京中心仓</v>
@@ -15920,10 +15920,10 @@
         <v>手机</v>
       </c>
       <c r="K408" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L408" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="409">
@@ -15958,7 +15958,7 @@
         <v>手机</v>
       </c>
       <c r="K409" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L409" t="str">
         <v>合肥中心仓</v>
@@ -15996,7 +15996,7 @@
         <v>笔记本</v>
       </c>
       <c r="K410" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L410" t="str">
         <v>合肥中心仓</v>
@@ -16034,7 +16034,7 @@
         <v>手机</v>
       </c>
       <c r="K411" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L411" t="str">
         <v/>
@@ -16072,7 +16072,7 @@
         <v>手机</v>
       </c>
       <c r="K412" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L412" t="str">
         <v>郑州中心仓</v>
@@ -16110,7 +16110,7 @@
         <v>手机</v>
       </c>
       <c r="K413" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L413" t="str">
         <v>南昌中心仓</v>
@@ -16148,7 +16148,7 @@
         <v>手机</v>
       </c>
       <c r="K414" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L414" t="str">
         <v/>
@@ -16191,7 +16191,7 @@
         <v>手机</v>
       </c>
       <c r="K415" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L415" t="str">
         <v>沈阳中心仓</v>
@@ -16229,7 +16229,7 @@
         <v>手机</v>
       </c>
       <c r="K416" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L416" t="str">
         <v>深圳中心仓</v>
@@ -16267,7 +16267,7 @@
         <v>手机</v>
       </c>
       <c r="K417" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L417" t="str">
         <v/>
@@ -16305,10 +16305,10 @@
         <v>手机</v>
       </c>
       <c r="K418" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L418" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="419" xml:space="preserve">
@@ -16344,10 +16344,10 @@
         <v>手机</v>
       </c>
       <c r="K419" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L419" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="420">
@@ -16382,10 +16382,10 @@
         <v>手机</v>
       </c>
       <c r="K420" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L420" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="421">
@@ -16420,10 +16420,10 @@
         <v>手机</v>
       </c>
       <c r="K421" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L421" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="422">
@@ -16458,10 +16458,10 @@
         <v>手机</v>
       </c>
       <c r="K422" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L422" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="423">
@@ -16496,7 +16496,7 @@
         <v>手机</v>
       </c>
       <c r="K423" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L423" t="str">
         <v>成都中心仓</v>
@@ -16534,7 +16534,7 @@
         <v>手机</v>
       </c>
       <c r="K424" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L424" t="str">
         <v>合肥中心仓</v>
@@ -16572,10 +16572,10 @@
         <v>手机</v>
       </c>
       <c r="K425" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L425" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="426">
@@ -16610,7 +16610,7 @@
         <v>手机</v>
       </c>
       <c r="K426" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L426" t="str">
         <v/>
@@ -16648,10 +16648,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K427" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L427" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="428">
@@ -16686,7 +16686,7 @@
         <v>手机</v>
       </c>
       <c r="K428" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L428" t="str">
         <v>广州中心仓</v>
@@ -16724,10 +16724,10 @@
         <v>手机</v>
       </c>
       <c r="K429" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L429" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="430">
@@ -16762,10 +16762,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K430" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L430" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="431">
@@ -16800,10 +16800,10 @@
         <v>手机</v>
       </c>
       <c r="K431" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L431" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="432">
@@ -16838,7 +16838,7 @@
         <v>手机</v>
       </c>
       <c r="K432" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L432" t="str">
         <v/>
@@ -16876,7 +16876,7 @@
         <v>手机</v>
       </c>
       <c r="K433" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L433" t="str">
         <v/>
@@ -16914,7 +16914,7 @@
         <v>手机</v>
       </c>
       <c r="K434" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L434" t="str">
         <v/>
@@ -16952,7 +16952,7 @@
         <v>手机</v>
       </c>
       <c r="K435" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L435" t="str">
         <v/>
@@ -16990,7 +16990,7 @@
         <v>手机</v>
       </c>
       <c r="K436" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L436" t="str">
         <v>杭州中心仓</v>
@@ -17028,10 +17028,10 @@
         <v>手机</v>
       </c>
       <c r="K437" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L437" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="438">
@@ -17066,7 +17066,7 @@
         <v>手机</v>
       </c>
       <c r="K438" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L438" t="str">
         <v>南昌中心仓</v>
@@ -17104,10 +17104,10 @@
         <v>手机</v>
       </c>
       <c r="K439" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L439" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="440">
@@ -17142,7 +17142,7 @@
         <v>手机</v>
       </c>
       <c r="K440" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L440" t="str">
         <v>石家庄中心仓</v>
@@ -17180,7 +17180,7 @@
         <v>手机</v>
       </c>
       <c r="K441" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L441" t="str">
         <v>杭州中心仓</v>
@@ -17218,7 +17218,7 @@
         <v>手机</v>
       </c>
       <c r="K442" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L442" t="str">
         <v/>
@@ -17256,7 +17256,7 @@
         <v>手机</v>
       </c>
       <c r="K443" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L443" t="str">
         <v/>
@@ -17294,7 +17294,7 @@
         <v>手机</v>
       </c>
       <c r="K444" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L444" t="str">
         <v/>
@@ -17332,7 +17332,7 @@
         <v>手机</v>
       </c>
       <c r="K445" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L445" t="str">
         <v/>
@@ -17370,7 +17370,7 @@
         <v>手机</v>
       </c>
       <c r="K446" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L446" t="str">
         <v>石家庄中心仓</v>
@@ -17408,10 +17408,10 @@
         <v>手机</v>
       </c>
       <c r="K447" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L447" t="str">
-        <v/>
+        <v>济南中心仓</v>
       </c>
     </row>
     <row r="448">
@@ -17446,10 +17446,10 @@
         <v>单电/微单套机</v>
       </c>
       <c r="K448" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L448" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="449">
@@ -17484,10 +17484,10 @@
         <v>手机</v>
       </c>
       <c r="K449" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L449" t="str">
-        <v/>
+        <v>合肥中心仓</v>
       </c>
     </row>
     <row r="450">
@@ -17522,10 +17522,10 @@
         <v>手机</v>
       </c>
       <c r="K450" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L450" t="str">
-        <v/>
+        <v>济南中心仓</v>
       </c>
     </row>
     <row r="451">
@@ -17560,7 +17560,7 @@
         <v>手机</v>
       </c>
       <c r="K451" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L451" t="str">
         <v>合肥中心仓</v>
@@ -17598,7 +17598,7 @@
         <v>手机</v>
       </c>
       <c r="K452" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L452" t="str">
         <v>济南中心仓</v>
@@ -17637,7 +17637,7 @@
         <v>手机</v>
       </c>
       <c r="K453" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L453" t="str">
         <v>成都中心仓</v>
@@ -17675,10 +17675,10 @@
         <v>手机</v>
       </c>
       <c r="K454" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L454" t="str">
-        <v/>
+        <v>郑州中心仓</v>
       </c>
     </row>
     <row r="455">
@@ -17713,7 +17713,7 @@
         <v>手机</v>
       </c>
       <c r="K455" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L455" t="str">
         <v>合肥中心仓</v>
@@ -17751,7 +17751,7 @@
         <v>手机</v>
       </c>
       <c r="K456" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L456" t="str">
         <v>深圳中心仓</v>
@@ -17789,7 +17789,7 @@
         <v>手机</v>
       </c>
       <c r="K457" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L457" t="str">
         <v>深圳中心仓</v>
@@ -17827,10 +17827,10 @@
         <v>手机</v>
       </c>
       <c r="K458" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L458" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="459">
@@ -17865,10 +17865,10 @@
         <v>手机</v>
       </c>
       <c r="K459" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L459" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="460">
@@ -17903,10 +17903,10 @@
         <v>手机</v>
       </c>
       <c r="K460" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L460" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="461">
@@ -17941,10 +17941,10 @@
         <v>手机</v>
       </c>
       <c r="K461" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L461" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="462">
@@ -17979,10 +17979,10 @@
         <v>手机</v>
       </c>
       <c r="K462" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L462" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
     <row r="463">
@@ -18017,7 +18017,7 @@
         <v>手机</v>
       </c>
       <c r="K463" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L463" t="str">
         <v>合肥中心仓</v>
@@ -18055,7 +18055,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K464" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L464" t="str">
         <v>深圳中心仓</v>
@@ -18093,7 +18093,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K465" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L465" t="str">
         <v>深圳中心仓</v>
@@ -18131,7 +18131,7 @@
         <v>手机</v>
       </c>
       <c r="K466" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L466" t="str">
         <v>天津中心仓</v>
@@ -18169,7 +18169,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K467" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L467" t="str">
         <v>南昌中心仓</v>
@@ -18207,10 +18207,10 @@
         <v>手机</v>
       </c>
       <c r="K468" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L468" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="469" xml:space="preserve">
@@ -18246,10 +18246,10 @@
         <v>智能手表</v>
       </c>
       <c r="K469" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L469" t="str">
-        <v/>
+        <v>成都中心仓</v>
       </c>
     </row>
     <row r="470">
@@ -18284,10 +18284,10 @@
         <v>手机</v>
       </c>
       <c r="K470" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L470" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="471">
@@ -18322,10 +18322,10 @@
         <v>手机</v>
       </c>
       <c r="K471" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L471" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="472">
@@ -18360,10 +18360,10 @@
         <v>手机</v>
       </c>
       <c r="K472" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L472" t="str">
-        <v/>
+        <v>沈阳中心仓</v>
       </c>
     </row>
     <row r="473">
@@ -18398,7 +18398,7 @@
         <v>平板电脑</v>
       </c>
       <c r="K473" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L473" t="str">
         <v>武汉中心仓</v>
@@ -18436,7 +18436,7 @@
         <v>手机</v>
       </c>
       <c r="K474" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L474" t="str">
         <v>南昌中心仓</v>
@@ -18474,10 +18474,10 @@
         <v>平板电脑</v>
       </c>
       <c r="K475" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L475" t="str">
-        <v/>
+        <v>昆明中心仓</v>
       </c>
     </row>
     <row r="476">
@@ -18512,10 +18512,10 @@
         <v>手机</v>
       </c>
       <c r="K476" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L476" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="477">
@@ -18550,10 +18550,10 @@
         <v>手机</v>
       </c>
       <c r="K477" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L477" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="478">
@@ -18588,7 +18588,7 @@
         <v>手机</v>
       </c>
       <c r="K478" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L478" t="str">
         <v>杭州中心仓</v>
@@ -18626,7 +18626,7 @@
         <v>手机</v>
       </c>
       <c r="K479" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L479" t="str">
         <v>南昌中心仓</v>
@@ -18664,7 +18664,7 @@
         <v>手机</v>
       </c>
       <c r="K480" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L480" t="str">
         <v>南昌中心仓</v>
@@ -18702,10 +18702,10 @@
         <v>手机</v>
       </c>
       <c r="K481" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L481" t="str">
-        <v/>
+        <v>长沙中心仓</v>
       </c>
     </row>
     <row r="482">
@@ -18740,7 +18740,7 @@
         <v>手机</v>
       </c>
       <c r="K482" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L482" t="str">
         <v>南昌中心仓</v>
@@ -18778,7 +18778,7 @@
         <v>手机</v>
       </c>
       <c r="K483" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L483" t="str">
         <v>重庆中心仓</v>
@@ -18816,7 +18816,7 @@
         <v>手机</v>
       </c>
       <c r="K484" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L484" t="str">
         <v/>
@@ -18854,10 +18854,10 @@
         <v>手机</v>
       </c>
       <c r="K485" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L485" t="str">
-        <v/>
+        <v>石家庄中心仓</v>
       </c>
     </row>
     <row r="486">
@@ -18892,7 +18892,7 @@
         <v>手机</v>
       </c>
       <c r="K486" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L486" t="str">
         <v>南京中心仓</v>
@@ -18930,7 +18930,7 @@
         <v>手机</v>
       </c>
       <c r="K487" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L487" t="str">
         <v>南京中心仓</v>
@@ -18968,7 +18968,7 @@
         <v>手机</v>
       </c>
       <c r="K488" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L488" t="str">
         <v>西安中心仓</v>
@@ -19006,7 +19006,7 @@
         <v>手机</v>
       </c>
       <c r="K489" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L489" t="str">
         <v>南京中心仓</v>
@@ -19044,7 +19044,7 @@
         <v>手机</v>
       </c>
       <c r="K490" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L490" t="str">
         <v>深圳中心仓</v>
@@ -19082,7 +19082,7 @@
         <v>手机</v>
       </c>
       <c r="K491" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L491" t="str">
         <v>南京中心仓</v>
@@ -19120,7 +19120,7 @@
         <v>手机</v>
       </c>
       <c r="K492" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L492" t="str">
         <v>昆明中心仓</v>
@@ -19158,7 +19158,7 @@
         <v>手机</v>
       </c>
       <c r="K493" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L493" t="str">
         <v>南京中心仓</v>
@@ -19196,7 +19196,7 @@
         <v>手机</v>
       </c>
       <c r="K494" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L494" t="str">
         <v>南京中心仓</v>
@@ -19234,10 +19234,10 @@
         <v>手机</v>
       </c>
       <c r="K495" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L495" t="str">
-        <v/>
+        <v>杭州中心仓</v>
       </c>
     </row>
     <row r="496">
@@ -19272,7 +19272,7 @@
         <v>手机</v>
       </c>
       <c r="K496" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L496" t="str">
         <v>济南中心仓</v>
@@ -19310,7 +19310,7 @@
         <v>手机</v>
       </c>
       <c r="K497" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L497" t="str">
         <v>杭州中心仓</v>
@@ -19348,7 +19348,7 @@
         <v>手机</v>
       </c>
       <c r="K498" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L498" t="str">
         <v>杭州中心仓</v>
@@ -19386,10 +19386,10 @@
         <v>手机</v>
       </c>
       <c r="K499" t="str">
-        <v>本地录入</v>
+        <v>入仓质检</v>
       </c>
       <c r="L499" t="str">
-        <v/>
+        <v>南京中心仓</v>
       </c>
     </row>
   </sheetData>

--- a/feedback-daily.xlsx
+++ b/feedback-daily.xlsx
@@ -472,7 +472,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L2" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L3" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L4" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="5">
@@ -586,7 +586,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L5" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="6">
@@ -624,7 +624,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L6" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L7" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="8">
@@ -700,7 +700,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L8" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="9">
@@ -776,7 +776,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L10" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="11">
@@ -814,7 +814,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="12">
@@ -852,7 +852,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L12" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="13">
@@ -890,7 +890,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L13" t="str">
-        <v>青岛中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="14">
@@ -928,7 +928,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L14" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="15">
@@ -966,7 +966,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L15" t="str">
-        <v>郑州中心仓</v>
+        <v>洛阳-李鹏远（已验机plus）</v>
       </c>
     </row>
     <row r="16">
@@ -1004,7 +1004,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L16" t="str">
-        <v>重庆中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="17">
@@ -1042,7 +1042,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L17" t="str">
-        <v>重庆中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="18">
@@ -1080,7 +1080,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L18" t="str">
-        <v>重庆中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="19">
@@ -1118,7 +1118,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L19" t="str">
-        <v>重庆中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="20">
@@ -1156,7 +1156,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L20" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="21">
@@ -1194,7 +1194,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L21" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="22">
@@ -1232,7 +1232,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L22" t="str">
-        <v>郑州中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="23">
@@ -1270,7 +1270,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L23" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="24">
@@ -1308,7 +1308,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L24" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="25">
@@ -1346,7 +1346,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L25" t="str">
-        <v>杭州中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="26">
@@ -1384,7 +1384,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L26" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="27">
@@ -1422,7 +1422,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L27" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="28">
@@ -1460,7 +1460,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L28" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="29">
@@ -1498,7 +1498,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L29" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="30">
@@ -1536,7 +1536,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L30" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="31">
@@ -1574,7 +1574,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L31" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="32">
@@ -1612,7 +1612,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L32" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="33">
@@ -1650,7 +1650,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L33" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="34">
@@ -1688,7 +1688,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L34" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="35">
@@ -1726,7 +1726,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L35" t="str">
-        <v>杭州中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="36">
@@ -1764,7 +1764,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L36" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="37">
@@ -1802,7 +1802,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L37" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="38">
@@ -1840,7 +1840,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L38" t="str">
-        <v>上海中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="39">
@@ -1878,7 +1878,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L39" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="40">
@@ -1916,7 +1916,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L40" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="41">
@@ -1954,7 +1954,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L41" t="str">
-        <v>广州中心仓</v>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="42">
@@ -1992,7 +1992,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L42" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="43">
@@ -2030,7 +2030,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L43" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="44">
@@ -2068,7 +2068,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L44" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="45">
@@ -2144,7 +2144,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L46" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="47">
@@ -2182,7 +2182,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L47" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="48">
@@ -2220,7 +2220,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L48" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="49">
@@ -2258,7 +2258,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L49" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="50">
@@ -2296,7 +2296,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L50" t="str">
-        <v>郑州中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="51">
@@ -2334,7 +2334,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L51" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="52">
@@ -2372,7 +2372,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L52" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="53">
@@ -2410,7 +2410,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L53" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="54">
@@ -2448,7 +2448,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L54" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="55">
@@ -2486,7 +2486,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L55" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="56">
@@ -2524,7 +2524,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L56" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="57">
@@ -2562,7 +2562,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L57" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -2603,7 +2603,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L58" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="59">
@@ -2641,7 +2641,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L59" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="60">
@@ -2679,7 +2679,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L60" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="61">
@@ -2717,7 +2717,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L61" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="62">
@@ -2755,7 +2755,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L62" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="63">
@@ -2793,7 +2793,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L63" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="64">
@@ -2831,7 +2831,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L64" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="65">
@@ -2907,7 +2907,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L66" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="67">
@@ -2945,7 +2945,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L67" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="68">
@@ -2983,7 +2983,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L68" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="69">
@@ -3021,7 +3021,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L69" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="70">
@@ -3059,7 +3059,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L70" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="71">
@@ -3097,7 +3097,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L71" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="72">
@@ -3135,7 +3135,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L72" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="73">
@@ -3173,7 +3173,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L73" t="str">
-        <v>南京中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="74">
@@ -3211,7 +3211,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L74" t="str">
-        <v>南京中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="75">
@@ -3249,7 +3249,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L75" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="76">
@@ -3287,7 +3287,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L76" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="77">
@@ -3325,7 +3325,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L77" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="78">
@@ -3363,7 +3363,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L78" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="79">
@@ -3401,7 +3401,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L79" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="80">
@@ -3439,7 +3439,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L80" t="str">
-        <v>深圳中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="81">
@@ -3477,7 +3477,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L81" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="82">
@@ -3553,7 +3553,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L83" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="84">
@@ -3591,7 +3591,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L84" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="85">
@@ -3629,7 +3629,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L85" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="86">
@@ -3667,7 +3667,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L86" t="str">
-        <v>深圳中心仓</v>
+        <v>转转-深圳智能验机中心</v>
       </c>
     </row>
     <row r="87">
@@ -3705,7 +3705,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L87" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="88">
@@ -3743,7 +3743,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L88" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="89">
@@ -3781,7 +3781,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L89" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
@@ -3820,7 +3820,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L90" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
@@ -3859,7 +3859,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L91" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="92">
@@ -3897,7 +3897,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L92" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="93">
@@ -3935,7 +3935,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L93" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="94">
@@ -3973,7 +3973,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L94" t="str">
-        <v>南京中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="95">
@@ -4011,7 +4011,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L95" t="str">
-        <v>南京中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="96">
@@ -4049,7 +4049,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L96" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="97" xml:space="preserve">
@@ -4088,7 +4088,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L97" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="98">
@@ -4126,7 +4126,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L98" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="99">
@@ -4164,7 +4164,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L99" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="100">
@@ -4202,7 +4202,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L100" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="101">
@@ -4240,7 +4240,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L101" t="str">
-        <v>郑州中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="102">
@@ -4278,7 +4278,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L102" t="str">
-        <v>郑州中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="103">
@@ -4316,7 +4316,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L103" t="str">
-        <v>郑州中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="104">
@@ -4354,7 +4354,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L104" t="str">
-        <v>广州中心仓</v>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="105">
@@ -4392,7 +4392,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L105" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="106">
@@ -4430,7 +4430,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L106" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="107">
@@ -4468,7 +4468,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L107" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="108" xml:space="preserve">
@@ -4507,7 +4507,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L108" t="str">
-        <v>深圳中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="109">
@@ -4545,7 +4545,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L109" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="110">
@@ -4583,7 +4583,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L110" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="111">
@@ -4621,7 +4621,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L111" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="112" xml:space="preserve">
@@ -4660,7 +4660,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L112" t="str">
-        <v>沈阳中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="113">
@@ -4698,7 +4698,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L113" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="114">
@@ -4736,7 +4736,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L114" t="str">
-        <v/>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="115">
@@ -4774,7 +4774,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L115" t="str">
-        <v/>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="116">
@@ -4812,7 +4812,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L116" t="str">
-        <v/>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="117">
@@ -4850,7 +4850,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L117" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="118">
@@ -4888,7 +4888,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L118" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="119">
@@ -4926,7 +4926,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L119" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="120">
@@ -4964,7 +4964,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L120" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="121">
@@ -5002,7 +5002,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L121" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="122">
@@ -5040,7 +5040,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L122" t="str">
-        <v>南昌中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="123">
@@ -5078,7 +5078,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L123" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="124">
@@ -5116,7 +5116,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L124" t="str">
-        <v>长沙中心仓</v>
+        <v>长沙库</v>
       </c>
     </row>
     <row r="125">
@@ -5193,7 +5193,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L126" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="127">
@@ -5231,7 +5231,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L127" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="128">
@@ -5269,7 +5269,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L128" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="129">
@@ -5307,7 +5307,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L129" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="130">
@@ -5383,7 +5383,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L131" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="132">
@@ -5421,7 +5421,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L132" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="133">
@@ -5459,7 +5459,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L133" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="134">
@@ -5497,7 +5497,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L134" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="135">
@@ -5535,7 +5535,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L135" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="136">
@@ -5573,7 +5573,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L136" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="137">
@@ -5611,7 +5611,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L137" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="138">
@@ -5649,7 +5649,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L138" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="139">
@@ -5687,7 +5687,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L139" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="140">
@@ -5725,7 +5725,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L140" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="141">
@@ -5763,7 +5763,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L141" t="str">
-        <v>合肥中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="142">
@@ -5801,7 +5801,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L142" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="143">
@@ -5839,7 +5839,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L143" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="144">
@@ -5915,7 +5915,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L145" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="146">
@@ -5953,7 +5953,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L146" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="147">
@@ -5991,7 +5991,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L147" t="str">
-        <v>合肥中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="148">
@@ -6029,7 +6029,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L148" t="str">
-        <v>合肥中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="149">
@@ -6067,7 +6067,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L149" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="150">
@@ -6143,7 +6143,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L151" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="152">
@@ -6181,7 +6181,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L152" t="str">
-        <v>北京中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="153">
@@ -6219,7 +6219,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L153" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="154">
@@ -6257,7 +6257,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L154" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="155">
@@ -6295,7 +6295,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L155" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="156">
@@ -6333,7 +6333,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L156" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="157">
@@ -6371,7 +6371,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L157" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="158">
@@ -6409,7 +6409,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L158" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="159">
@@ -6447,7 +6447,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L159" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="160">
@@ -6485,7 +6485,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L160" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="161">
@@ -6523,7 +6523,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L161" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="162">
@@ -6561,7 +6561,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L162" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="163">
@@ -6599,7 +6599,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L163" t="str">
-        <v>北京中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="164">
@@ -6637,7 +6637,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L164" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="165">
@@ -6675,7 +6675,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L165" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="166">
@@ -6713,7 +6713,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L166" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="167">
@@ -6751,7 +6751,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L167" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="168">
@@ -6789,7 +6789,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L168" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="169">
@@ -6827,7 +6827,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L169" t="str">
-        <v>郑州中心仓</v>
+        <v>洛阳-李鹏远（已验机plus）</v>
       </c>
     </row>
     <row r="170">
@@ -6865,7 +6865,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L170" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="171">
@@ -6903,7 +6903,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L171" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="172">
@@ -6941,7 +6941,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L172" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="173">
@@ -6979,7 +6979,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L173" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="174">
@@ -7017,7 +7017,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L174" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="175">
@@ -7055,7 +7055,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L175" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="176">
@@ -7093,7 +7093,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L176" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="177">
@@ -7131,7 +7131,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L177" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="178">
@@ -7169,7 +7169,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L178" t="str">
-        <v>长沙中心仓</v>
+        <v>长沙库</v>
       </c>
     </row>
     <row r="179">
@@ -7359,7 +7359,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L183" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="184">
@@ -7397,7 +7397,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L184" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="185">
@@ -7435,7 +7435,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L185" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="186">
@@ -7473,7 +7473,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L186" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="187">
@@ -7549,7 +7549,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L188" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="189">
@@ -7587,7 +7587,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L189" t="str">
-        <v>重庆中心仓</v>
+        <v>重庆库</v>
       </c>
     </row>
     <row r="190">
@@ -7625,7 +7625,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L190" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="191">
@@ -7663,7 +7663,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L191" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="192">
@@ -7701,7 +7701,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L192" t="str">
-        <v>天津中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="193">
@@ -7739,7 +7739,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L193" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="194">
@@ -7777,7 +7777,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L194" t="str">
-        <v>南京中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="195">
@@ -7815,7 +7815,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L195" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="196">
@@ -7853,7 +7853,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L196" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="197">
@@ -7891,7 +7891,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L197" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="198">
@@ -7929,7 +7929,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L198" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="199">
@@ -7967,7 +7967,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L199" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="200">
@@ -8005,7 +8005,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L200" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="201">
@@ -8043,7 +8043,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L201" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="202">
@@ -8081,7 +8081,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L202" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="203">
@@ -8119,7 +8119,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L203" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="204">
@@ -8157,7 +8157,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L204" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="205">
@@ -8195,7 +8195,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L205" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="206">
@@ -8271,7 +8271,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L207" t="str">
-        <v>南昌中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="208">
@@ -8309,7 +8309,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L208" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="209">
@@ -8347,7 +8347,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L209" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="210">
@@ -8385,7 +8385,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L210" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="211">
@@ -8613,7 +8613,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L216" t="str">
-        <v>深圳中心仓</v>
+        <v>深圳-迟恭彦（自质检2.0）</v>
       </c>
     </row>
     <row r="217">
@@ -8651,7 +8651,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L217" t="str">
-        <v>深圳中心仓</v>
+        <v>深圳-迟恭彦（自质检2.0）</v>
       </c>
     </row>
     <row r="218">
@@ -8689,7 +8689,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L218" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="219">
@@ -8727,7 +8727,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L219" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="220">
@@ -8765,7 +8765,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L220" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="221">
@@ -8803,7 +8803,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L221" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="222">
@@ -8841,7 +8841,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L222" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="223">
@@ -8879,7 +8879,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L223" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="224">
@@ -8917,7 +8917,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L224" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="225">
@@ -8955,7 +8955,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L225" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="226">
@@ -8993,7 +8993,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L226" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="227">
@@ -9031,7 +9031,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L227" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="228">
@@ -9069,7 +9069,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L228" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="229">
@@ -9107,7 +9107,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L229" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="230">
@@ -9145,7 +9145,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L230" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="231">
@@ -9183,7 +9183,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L231" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="232">
@@ -9221,7 +9221,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L232" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="233">
@@ -9259,7 +9259,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L233" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="234">
@@ -9297,7 +9297,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L234" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="235">
@@ -9335,7 +9335,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L235" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="236">
@@ -9373,7 +9373,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L236" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="237">
@@ -9411,7 +9411,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L237" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="238">
@@ -9449,7 +9449,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L238" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="239">
@@ -9487,7 +9487,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L239" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="240">
@@ -9525,7 +9525,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L240" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="241">
@@ -9563,7 +9563,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L241" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="242">
@@ -9601,7 +9601,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L242" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="243">
@@ -9639,7 +9639,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L243" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="244">
@@ -9677,7 +9677,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L244" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="245">
@@ -9715,7 +9715,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L245" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="246">
@@ -9753,7 +9753,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L246" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="247">
@@ -9791,7 +9791,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L247" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="248">
@@ -9829,7 +9829,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L248" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="249">
@@ -9867,7 +9867,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L249" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="250">
@@ -9905,7 +9905,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L250" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="251">
@@ -9943,7 +9943,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L251" t="str">
-        <v/>
+        <v>福建-魏女（已验机2.0）</v>
       </c>
     </row>
     <row r="252">
@@ -9981,7 +9981,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L252" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="253">
@@ -10019,7 +10019,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L253" t="str">
-        <v>济南中心仓</v>
+        <v>青岛后验中心仓</v>
       </c>
     </row>
     <row r="254">
@@ -10057,7 +10057,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L254" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="255">
@@ -10095,7 +10095,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L255" t="str">
-        <v>重庆中心仓</v>
+        <v>重庆库</v>
       </c>
     </row>
     <row r="256">
@@ -10133,7 +10133,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L256" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="257">
@@ -10171,7 +10171,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L257" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="258">
@@ -10209,7 +10209,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L258" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="259">
@@ -10247,7 +10247,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L259" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="260">
@@ -10285,7 +10285,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L260" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="261">
@@ -10323,7 +10323,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L261" t="str">
-        <v>广州中心仓</v>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="262">
@@ -10361,7 +10361,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L262" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="263">
@@ -10399,7 +10399,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L263" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="264">
@@ -10437,7 +10437,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L264" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="265">
@@ -10552,7 +10552,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L267" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="268" xml:space="preserve">
@@ -10591,7 +10591,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L268" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="269">
@@ -10629,7 +10629,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L269" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="270">
@@ -10667,7 +10667,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L270" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="271">
@@ -10705,7 +10705,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L271" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="272">
@@ -10743,7 +10743,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L272" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="273">
@@ -10781,7 +10781,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L273" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="274">
@@ -10819,7 +10819,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L274" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="275">
@@ -10857,7 +10857,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L275" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="276">
@@ -10895,7 +10895,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L276" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="277">
@@ -11009,7 +11009,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L279" t="str">
-        <v>西安中心仓</v>
+        <v>西安库</v>
       </c>
     </row>
     <row r="280">
@@ -11047,7 +11047,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L280" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="281">
@@ -11085,7 +11085,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L281" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="282" xml:space="preserve">
@@ -11124,7 +11124,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L282" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="283">
@@ -11162,7 +11162,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L283" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="284">
@@ -11200,7 +11200,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L284" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="285">
@@ -11238,7 +11238,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L285" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="286">
@@ -11580,7 +11580,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L294" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="295">
@@ -11618,7 +11618,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L295" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="296">
@@ -11656,7 +11656,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L296" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="297">
@@ -11694,7 +11694,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L297" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="298">
@@ -11732,7 +11732,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L298" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="299">
@@ -11808,7 +11808,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L300" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="301">
@@ -11846,7 +11846,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L301" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="302">
@@ -11884,7 +11884,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L302" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="303">
@@ -11922,7 +11922,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L303" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="304">
@@ -11960,7 +11960,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L304" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="305">
@@ -11998,7 +11998,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L305" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="306">
@@ -12074,7 +12074,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L307" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="308">
@@ -12150,7 +12150,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L309" t="str">
-        <v/>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="310">
@@ -12188,7 +12188,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L310" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="311">
@@ -12226,7 +12226,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L311" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="312">
@@ -12264,7 +12264,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L312" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="313">
@@ -12340,7 +12340,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L314" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="315">
@@ -12378,7 +12378,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L315" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="316">
@@ -12416,7 +12416,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L316" t="str">
-        <v>长沙中心仓</v>
+        <v>长沙库</v>
       </c>
     </row>
     <row r="317">
@@ -12454,7 +12454,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L317" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="318">
@@ -12492,7 +12492,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L318" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="319">
@@ -12530,7 +12530,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L319" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="320">
@@ -12568,7 +12568,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L320" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="321">
@@ -12606,7 +12606,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L321" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="322">
@@ -12644,7 +12644,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L322" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="323">
@@ -12682,7 +12682,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L323" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="324">
@@ -12720,7 +12720,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L324" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="325">
@@ -12949,7 +12949,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L330" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="331">
@@ -13215,7 +13215,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L337" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="338">
@@ -13253,7 +13253,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L338" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="339">
@@ -13291,7 +13291,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L339" t="str">
-        <v>沈阳中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="340">
@@ -13329,7 +13329,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L340" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="341">
@@ -13367,7 +13367,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L341" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="342">
@@ -13405,7 +13405,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L342" t="str">
-        <v>重庆中心仓</v>
+        <v>重庆库</v>
       </c>
     </row>
     <row r="343">
@@ -13443,7 +13443,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L343" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="344">
@@ -13481,7 +13481,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L344" t="str">
-        <v>沈阳中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="345">
@@ -13519,7 +13519,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L345" t="str">
-        <v>北京中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="346">
@@ -13557,7 +13557,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L346" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="347">
@@ -13595,7 +13595,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L347" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="348">
@@ -13633,7 +13633,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L348" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="349">
@@ -13671,7 +13671,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L349" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="350">
@@ -13709,7 +13709,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L350" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="351">
@@ -13747,7 +13747,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L351" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="352">
@@ -13785,7 +13785,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L352" t="str">
-        <v>重庆中心仓</v>
+        <v>重庆库</v>
       </c>
     </row>
     <row r="353" xml:space="preserve">
@@ -13827,7 +13827,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L353" t="str">
-        <v>西安中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="354">
@@ -13865,7 +13865,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L354" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="355">
@@ -13903,7 +13903,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L355" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="356">
@@ -13941,7 +13941,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L356" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="357">
@@ -13979,7 +13979,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L357" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="358">
@@ -14017,7 +14017,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L358" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="359">
@@ -14055,7 +14055,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L359" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="360">
@@ -14093,7 +14093,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L360" t="str">
-        <v>深圳中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="361">
@@ -14131,7 +14131,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L361" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="362">
@@ -14169,7 +14169,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L362" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="363">
@@ -14207,7 +14207,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L363" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="364">
@@ -14321,7 +14321,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L366" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="367">
@@ -14359,7 +14359,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L367" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="368">
@@ -14397,7 +14397,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L368" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="369">
@@ -14435,7 +14435,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L369" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="370">
@@ -14473,7 +14473,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L370" t="str">
-        <v>成都中心仓</v>
+        <v>转转-深圳智能验机中心</v>
       </c>
     </row>
     <row r="371">
@@ -14511,7 +14511,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L371" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="372" xml:space="preserve">
@@ -14550,7 +14550,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L372" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="373">
@@ -14588,7 +14588,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L373" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="374">
@@ -14626,7 +14626,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L374" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="375">
@@ -14664,7 +14664,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L375" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="376">
@@ -14702,7 +14702,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L376" t="str">
-        <v>福州中心仓</v>
+        <v>福州库</v>
       </c>
     </row>
     <row r="377">
@@ -14740,7 +14740,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L377" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="378">
@@ -14778,7 +14778,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L378" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="379">
@@ -14816,7 +14816,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L379" t="str">
-        <v>济南中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="380" xml:space="preserve">
@@ -14857,7 +14857,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L380" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="381">
@@ -14895,7 +14895,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L381" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="382">
@@ -14933,7 +14933,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L382" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="383">
@@ -14971,7 +14971,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L383" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="384">
@@ -15009,7 +15009,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L384" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="385">
@@ -15085,7 +15085,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L386" t="str">
-        <v>合肥中心仓</v>
+        <v>转转-深圳智能验机中心</v>
       </c>
     </row>
     <row r="387">
@@ -15161,7 +15161,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L388" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="389">
@@ -15199,7 +15199,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L389" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="390">
@@ -15237,7 +15237,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L390" t="str">
-        <v>成都中心仓</v>
+        <v>转转-深圳智能验机中心</v>
       </c>
     </row>
     <row r="391">
@@ -15275,7 +15275,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L391" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="392" xml:space="preserve">
@@ -15315,7 +15315,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L392" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="393">
@@ -15353,7 +15353,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L393" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="394">
@@ -15391,7 +15391,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L394" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="395">
@@ -15429,7 +15429,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L395" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="396">
@@ -15467,7 +15467,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L396" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="397">
@@ -15505,7 +15505,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L397" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="398">
@@ -15543,7 +15543,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L398" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="399">
@@ -15581,7 +15581,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L399" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="400">
@@ -15619,7 +15619,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L400" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="401">
@@ -15657,7 +15657,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L401" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="402">
@@ -15695,7 +15695,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L402" t="str">
-        <v/>
+        <v>南京库</v>
       </c>
     </row>
     <row r="403">
@@ -15733,7 +15733,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L403" t="str">
-        <v/>
+        <v>南京库</v>
       </c>
     </row>
     <row r="404">
@@ -15771,7 +15771,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L404" t="str">
-        <v>西安中心仓</v>
+        <v>西安库</v>
       </c>
     </row>
     <row r="405">
@@ -15809,7 +15809,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L405" t="str">
-        <v>西安中心仓</v>
+        <v>西安库</v>
       </c>
     </row>
     <row r="406">
@@ -15847,7 +15847,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L406" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="407">
@@ -15885,7 +15885,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L407" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="408">
@@ -15923,7 +15923,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L408" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="409">
@@ -15961,7 +15961,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L409" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="410">
@@ -15999,7 +15999,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L410" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="411">
@@ -16037,7 +16037,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L411" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="412">
@@ -16075,7 +16075,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L412" t="str">
-        <v>郑州中心仓</v>
+        <v>转转-青岛智能验机中心</v>
       </c>
     </row>
     <row r="413">
@@ -16113,7 +16113,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L413" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="414">
@@ -16151,7 +16151,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L414" t="str">
-        <v/>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="415" xml:space="preserve">
@@ -16194,7 +16194,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L415" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="416">
@@ -16232,7 +16232,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L416" t="str">
-        <v>深圳中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="417">
@@ -16270,7 +16270,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L417" t="str">
-        <v/>
+        <v>重庆库</v>
       </c>
     </row>
     <row r="418">
@@ -16308,7 +16308,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L418" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="419" xml:space="preserve">
@@ -16347,7 +16347,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L419" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="420">
@@ -16385,7 +16385,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L420" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="421">
@@ -16423,7 +16423,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L421" t="str">
-        <v>石家庄中心仓</v>
+        <v>廊坊-于释尧（已验机2.0）</v>
       </c>
     </row>
     <row r="422">
@@ -16461,7 +16461,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L422" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="423">
@@ -16499,7 +16499,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L423" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="424">
@@ -16537,7 +16537,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L424" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="425">
@@ -16575,7 +16575,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L425" t="str">
-        <v>深圳中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="426">
@@ -16613,7 +16613,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L426" t="str">
-        <v/>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="427">
@@ -16651,7 +16651,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L427" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="428">
@@ -16689,7 +16689,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L428" t="str">
-        <v>广州中心仓</v>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="429">
@@ -16727,7 +16727,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L429" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="430">
@@ -16765,7 +16765,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L430" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="431">
@@ -16803,7 +16803,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L431" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="432">
@@ -16841,7 +16841,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L432" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="433">
@@ -16879,7 +16879,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L433" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="434">
@@ -16917,7 +16917,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L434" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="435">
@@ -16955,7 +16955,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L435" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="436">
@@ -16993,7 +16993,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L436" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="437">
@@ -17031,7 +17031,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L437" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="438">
@@ -17069,7 +17069,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L438" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="439">
@@ -17107,7 +17107,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L439" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="440">
@@ -17145,7 +17145,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L440" t="str">
-        <v>石家庄中心仓</v>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="441">
@@ -17183,7 +17183,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L441" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="442">
@@ -17221,7 +17221,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L442" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="443">
@@ -17259,7 +17259,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L443" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="444">
@@ -17297,7 +17297,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L444" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="445">
@@ -17335,7 +17335,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L445" t="str">
-        <v/>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="446">
@@ -17373,7 +17373,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L446" t="str">
-        <v>石家庄中心仓</v>
+        <v>深圳中心仓</v>
       </c>
     </row>
     <row r="447">
@@ -17411,7 +17411,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L447" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="448">
@@ -17449,7 +17449,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L448" t="str">
-        <v>深圳中心仓</v>
+        <v>济南-杨帆（多品类）</v>
       </c>
     </row>
     <row r="449">
@@ -17487,7 +17487,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L449" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="450">
@@ -17525,7 +17525,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L450" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="451">
@@ -17563,7 +17563,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L451" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="452">
@@ -17601,7 +17601,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L452" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="453" xml:space="preserve">
@@ -17640,7 +17640,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L453" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="454">
@@ -17678,7 +17678,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L454" t="str">
-        <v>郑州中心仓</v>
+        <v>郑州库</v>
       </c>
     </row>
     <row r="455">
@@ -17716,7 +17716,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L455" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="456">
@@ -17830,7 +17830,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L458" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="459">
@@ -17868,7 +17868,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L459" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="460">
@@ -17906,7 +17906,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L460" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="461">
@@ -17944,7 +17944,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L461" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="462">
@@ -17982,7 +17982,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L462" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="463">
@@ -18020,7 +18020,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L463" t="str">
-        <v>合肥中心仓</v>
+        <v>合肥库</v>
       </c>
     </row>
     <row r="464">
@@ -18134,7 +18134,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L466" t="str">
-        <v>天津中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="467">
@@ -18172,7 +18172,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L467" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="468">
@@ -18210,7 +18210,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L468" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="469" xml:space="preserve">
@@ -18249,7 +18249,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L469" t="str">
-        <v>成都中心仓</v>
+        <v>成都库</v>
       </c>
     </row>
     <row r="470">
@@ -18287,7 +18287,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L470" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="471">
@@ -18325,7 +18325,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L471" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="472">
@@ -18363,7 +18363,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L472" t="str">
-        <v>沈阳中心仓</v>
+        <v>沈阳库</v>
       </c>
     </row>
     <row r="473">
@@ -18401,7 +18401,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L473" t="str">
-        <v>武汉中心仓</v>
+        <v>武汉库</v>
       </c>
     </row>
     <row r="474">
@@ -18439,7 +18439,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L474" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="475">
@@ -18477,7 +18477,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L475" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="476">
@@ -18515,7 +18515,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L476" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="477">
@@ -18553,7 +18553,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L477" t="str">
-        <v>石家庄中心仓</v>
+        <v>转转-成都智能验机中心</v>
       </c>
     </row>
     <row r="478">
@@ -18591,7 +18591,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L478" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="479">
@@ -18629,7 +18629,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L479" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="480">
@@ -18667,7 +18667,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L480" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="481">
@@ -18705,7 +18705,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L481" t="str">
-        <v>长沙中心仓</v>
+        <v>长沙库</v>
       </c>
     </row>
     <row r="482">
@@ -18743,7 +18743,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L482" t="str">
-        <v>南昌中心仓</v>
+        <v>南昌库</v>
       </c>
     </row>
     <row r="483">
@@ -18781,7 +18781,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L483" t="str">
-        <v>重庆中心仓</v>
+        <v>重庆库</v>
       </c>
     </row>
     <row r="484">
@@ -18819,7 +18819,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L484" t="str">
-        <v/>
+        <v>转转-青岛智能验机中心</v>
       </c>
     </row>
     <row r="485">
@@ -18857,7 +18857,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L485" t="str">
-        <v>石家庄中心仓</v>
+        <v>石家庄库</v>
       </c>
     </row>
     <row r="486">
@@ -18895,7 +18895,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L486" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="487">
@@ -18933,7 +18933,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L487" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="488">
@@ -18971,7 +18971,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L488" t="str">
-        <v>西安中心仓</v>
+        <v>西安库</v>
       </c>
     </row>
     <row r="489">
@@ -19009,7 +19009,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L489" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="490">
@@ -19085,7 +19085,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L491" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="492">
@@ -19123,7 +19123,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L492" t="str">
-        <v>昆明中心仓</v>
+        <v>昆明库</v>
       </c>
     </row>
     <row r="493">
@@ -19161,7 +19161,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L493" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="494">
@@ -19199,7 +19199,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L494" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="495">
@@ -19237,7 +19237,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L495" t="str">
-        <v>杭州中心仓</v>
+        <v>杭州库</v>
       </c>
     </row>
     <row r="496">
@@ -19275,7 +19275,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L496" t="str">
-        <v>济南中心仓</v>
+        <v>济南库</v>
       </c>
     </row>
     <row r="497">
@@ -19313,7 +19313,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L497" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="498">
@@ -19351,7 +19351,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L498" t="str">
-        <v>杭州中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
     <row r="499">
@@ -19389,7 +19389,7 @@
         <v>入仓质检</v>
       </c>
       <c r="L499" t="str">
-        <v>南京中心仓</v>
+        <v>南京库</v>
       </c>
     </row>
   </sheetData>
